--- a/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>SPOT</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>12723800</v>
+        <v>14414100</v>
       </c>
       <c r="E8" s="3">
-        <v>10489800</v>
+        <v>12760100</v>
       </c>
       <c r="F8" s="3">
-        <v>8549800</v>
+        <v>10519800</v>
       </c>
       <c r="G8" s="3">
-        <v>7338900</v>
+        <v>8574200</v>
       </c>
       <c r="H8" s="3">
-        <v>5706000</v>
+        <v>7359900</v>
       </c>
       <c r="I8" s="3">
-        <v>4437700</v>
+        <v>5722300</v>
       </c>
       <c r="J8" s="3">
+        <v>4450300</v>
+      </c>
+      <c r="K8" s="3">
         <v>3202900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1980400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1225100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>892400</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9549100</v>
+        <v>10693800</v>
       </c>
       <c r="E9" s="3">
-        <v>7678500</v>
+        <v>9576400</v>
       </c>
       <c r="F9" s="3">
-        <v>6363500</v>
+        <v>7700500</v>
       </c>
       <c r="G9" s="3">
-        <v>5470600</v>
+        <v>6381700</v>
       </c>
       <c r="H9" s="3">
-        <v>4238000</v>
+        <v>5486200</v>
       </c>
       <c r="I9" s="3">
-        <v>3516500</v>
+        <v>4250100</v>
       </c>
       <c r="J9" s="3">
+        <v>3526500</v>
+      </c>
+      <c r="K9" s="3">
         <v>2767800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1749700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1028600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>739300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3174700</v>
+        <v>3720200</v>
       </c>
       <c r="E10" s="3">
-        <v>2811200</v>
+        <v>3183800</v>
       </c>
       <c r="F10" s="3">
-        <v>2186300</v>
+        <v>2819300</v>
       </c>
       <c r="G10" s="3">
-        <v>1868400</v>
+        <v>2192500</v>
       </c>
       <c r="H10" s="3">
-        <v>1468000</v>
+        <v>1873700</v>
       </c>
       <c r="I10" s="3">
-        <v>921200</v>
+        <v>1472200</v>
       </c>
       <c r="J10" s="3">
+        <v>923800</v>
+      </c>
+      <c r="K10" s="3">
         <v>435100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>230700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>196500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>153100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1461500</v>
+        <v>1665900</v>
       </c>
       <c r="E12" s="3">
-        <v>962400</v>
+        <v>1465700</v>
       </c>
       <c r="F12" s="3">
-        <v>888600</v>
+        <v>965100</v>
       </c>
       <c r="G12" s="3">
-        <v>652100</v>
+        <v>891200</v>
       </c>
       <c r="H12" s="3">
-        <v>534900</v>
+        <v>653900</v>
       </c>
       <c r="I12" s="3">
-        <v>429700</v>
+        <v>536400</v>
       </c>
       <c r="J12" s="3">
+        <v>430900</v>
+      </c>
+      <c r="K12" s="3">
         <v>224600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>138800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>128700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>87300</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,41 +961,44 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>364500</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -987,27 +1006,30 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>43400</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>27100</v>
+        <v>43500</v>
       </c>
       <c r="F15" s="3">
-        <v>19500</v>
+        <v>27200</v>
       </c>
       <c r="G15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="H15" s="3">
         <v>15200</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,15 +1045,18 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13438800</v>
+        <v>14899400</v>
       </c>
       <c r="E17" s="3">
-        <v>10387800</v>
+        <v>13477200</v>
       </c>
       <c r="F17" s="3">
-        <v>8867700</v>
+        <v>10417500</v>
       </c>
       <c r="G17" s="3">
-        <v>7418100</v>
+        <v>8893000</v>
       </c>
       <c r="H17" s="3">
-        <v>5753800</v>
+        <v>7439300</v>
       </c>
       <c r="I17" s="3">
-        <v>4846700</v>
+        <v>5770200</v>
       </c>
       <c r="J17" s="3">
+        <v>4860500</v>
+      </c>
+      <c r="K17" s="3">
         <v>3583800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2220200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1440700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1009600</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-715000</v>
+        <v>-485300</v>
       </c>
       <c r="E18" s="3">
-        <v>102000</v>
+        <v>-717100</v>
       </c>
       <c r="F18" s="3">
-        <v>-317900</v>
+        <v>102300</v>
       </c>
       <c r="G18" s="3">
-        <v>-79200</v>
+        <v>-318800</v>
       </c>
       <c r="H18" s="3">
-        <v>-47700</v>
+        <v>-79400</v>
       </c>
       <c r="I18" s="3">
-        <v>-409000</v>
+        <v>-47900</v>
       </c>
       <c r="J18" s="3">
+        <v>-410200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-380800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-239900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-215700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-117200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,80 +1179,84 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>358000</v>
+        <v>-22900</v>
       </c>
       <c r="E20" s="3">
-        <v>211600</v>
+        <v>359100</v>
       </c>
       <c r="F20" s="3">
-        <v>-406900</v>
+        <v>212200</v>
       </c>
       <c r="G20" s="3">
-        <v>-21700</v>
+        <v>-408000</v>
       </c>
       <c r="H20" s="3">
-        <v>-140000</v>
+        <v>-21800</v>
       </c>
       <c r="I20" s="3">
-        <v>-924400</v>
+        <v>-140400</v>
       </c>
       <c r="J20" s="3">
+        <v>-927100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-199600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>10200</v>
       </c>
       <c r="L20" s="3">
         <v>10200</v>
       </c>
       <c r="M20" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N20" s="3">
         <v>44300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-171500</v>
+        <v>-335200</v>
       </c>
       <c r="E21" s="3">
-        <v>451300</v>
+        <v>-170800</v>
       </c>
       <c r="F21" s="3">
-        <v>-604400</v>
+        <v>453500</v>
       </c>
       <c r="G21" s="3">
-        <v>-6500</v>
+        <v>-605400</v>
       </c>
       <c r="H21" s="3">
-        <v>-153000</v>
+        <v>-6000</v>
       </c>
       <c r="I21" s="3">
-        <v>-1274900</v>
+        <v>-153200</v>
       </c>
       <c r="J21" s="3">
+        <v>-1278200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-539300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-199600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,32 +1266,35 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>44500</v>
+        <v>41300</v>
       </c>
       <c r="E22" s="3">
-        <v>43400</v>
+        <v>44600</v>
       </c>
       <c r="F22" s="3">
-        <v>44500</v>
+        <v>43500</v>
       </c>
       <c r="G22" s="3">
-        <v>41200</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>44600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>41300</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>4400</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-401500</v>
+        <v>-549500</v>
       </c>
       <c r="E23" s="3">
-        <v>270200</v>
+        <v>-402600</v>
       </c>
       <c r="F23" s="3">
-        <v>-769300</v>
+        <v>270900</v>
       </c>
       <c r="G23" s="3">
-        <v>-142100</v>
+        <v>-771500</v>
       </c>
       <c r="H23" s="3">
-        <v>-187700</v>
+        <v>-142500</v>
       </c>
       <c r="I23" s="3">
-        <v>-1337800</v>
+        <v>-188200</v>
       </c>
       <c r="J23" s="3">
+        <v>-1341600</v>
+      </c>
+      <c r="K23" s="3">
         <v>-580500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-229700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-205500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-73000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>65100</v>
+        <v>29400</v>
       </c>
       <c r="E24" s="3">
-        <v>307100</v>
+        <v>65300</v>
       </c>
       <c r="F24" s="3">
-        <v>-138900</v>
+        <v>307900</v>
       </c>
       <c r="G24" s="3">
-        <v>59700</v>
+        <v>-139300</v>
       </c>
       <c r="H24" s="3">
-        <v>-103100</v>
+        <v>59800</v>
       </c>
       <c r="I24" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-466600</v>
+        <v>-578900</v>
       </c>
       <c r="E26" s="3">
-        <v>-36900</v>
+        <v>-467900</v>
       </c>
       <c r="F26" s="3">
-        <v>-630400</v>
+        <v>-37000</v>
       </c>
       <c r="G26" s="3">
-        <v>-201800</v>
+        <v>-632200</v>
       </c>
       <c r="H26" s="3">
-        <v>-84600</v>
+        <v>-202400</v>
       </c>
       <c r="I26" s="3">
-        <v>-1340000</v>
+        <v>-84900</v>
       </c>
       <c r="J26" s="3">
+        <v>-1343800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-584800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-234800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-212300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-75400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-466600</v>
+        <v>-578900</v>
       </c>
       <c r="E27" s="3">
-        <v>-36900</v>
+        <v>-467900</v>
       </c>
       <c r="F27" s="3">
-        <v>-630400</v>
+        <v>-37000</v>
       </c>
       <c r="G27" s="3">
-        <v>-201800</v>
+        <v>-632200</v>
       </c>
       <c r="H27" s="3">
-        <v>-84600</v>
+        <v>-202400</v>
       </c>
       <c r="I27" s="3">
-        <v>-1340000</v>
+        <v>-84900</v>
       </c>
       <c r="J27" s="3">
+        <v>-1343800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-584800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-234800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-212300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-75400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-358000</v>
+        <v>22900</v>
       </c>
       <c r="E32" s="3">
-        <v>-211600</v>
+        <v>-359100</v>
       </c>
       <c r="F32" s="3">
-        <v>406900</v>
+        <v>-212200</v>
       </c>
       <c r="G32" s="3">
-        <v>21700</v>
+        <v>408000</v>
       </c>
       <c r="H32" s="3">
-        <v>140000</v>
+        <v>21800</v>
       </c>
       <c r="I32" s="3">
-        <v>924400</v>
+        <v>140400</v>
       </c>
       <c r="J32" s="3">
+        <v>927100</v>
+      </c>
+      <c r="K32" s="3">
         <v>199600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-10200</v>
       </c>
       <c r="L32" s="3">
         <v>-10200</v>
       </c>
       <c r="M32" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-44300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-466600</v>
+        <v>-578900</v>
       </c>
       <c r="E33" s="3">
-        <v>-36900</v>
+        <v>-467900</v>
       </c>
       <c r="F33" s="3">
-        <v>-630400</v>
+        <v>-37000</v>
       </c>
       <c r="G33" s="3">
-        <v>-201800</v>
+        <v>-632200</v>
       </c>
       <c r="H33" s="3">
-        <v>-84600</v>
+        <v>-202400</v>
       </c>
       <c r="I33" s="3">
-        <v>-1340000</v>
+        <v>-84900</v>
       </c>
       <c r="J33" s="3">
+        <v>-1343800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-584800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-234800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-212300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-75400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-466600</v>
+        <v>-578900</v>
       </c>
       <c r="E35" s="3">
-        <v>-36900</v>
+        <v>-467900</v>
       </c>
       <c r="F35" s="3">
-        <v>-630400</v>
+        <v>-37000</v>
       </c>
       <c r="G35" s="3">
-        <v>-201800</v>
+        <v>-632200</v>
       </c>
       <c r="H35" s="3">
-        <v>-84600</v>
+        <v>-202400</v>
       </c>
       <c r="I35" s="3">
-        <v>-1340000</v>
+        <v>-84900</v>
       </c>
       <c r="J35" s="3">
+        <v>-1343800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-584800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-234800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-212300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-75400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,122 +1987,129 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2694100</v>
+        <v>3388300</v>
       </c>
       <c r="E41" s="3">
-        <v>2977200</v>
+        <v>2701800</v>
       </c>
       <c r="F41" s="3">
-        <v>1248800</v>
+        <v>2985700</v>
       </c>
       <c r="G41" s="3">
-        <v>1155500</v>
+        <v>1252400</v>
       </c>
       <c r="H41" s="3">
-        <v>966700</v>
+        <v>1158800</v>
       </c>
       <c r="I41" s="3">
-        <v>517500</v>
+        <v>969500</v>
       </c>
       <c r="J41" s="3">
+        <v>519000</v>
+      </c>
+      <c r="K41" s="3">
         <v>819200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>609400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>232600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>260800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>940700</v>
+        <v>1196900</v>
       </c>
       <c r="E42" s="3">
-        <v>820300</v>
+        <v>943400</v>
       </c>
       <c r="F42" s="3">
-        <v>646700</v>
+        <v>822600</v>
       </c>
       <c r="G42" s="3">
-        <v>750800</v>
+        <v>648500</v>
       </c>
       <c r="H42" s="3">
-        <v>992800</v>
+        <v>753000</v>
       </c>
       <c r="I42" s="3">
-        <v>1119700</v>
+        <v>995600</v>
       </c>
       <c r="J42" s="3">
+        <v>1122900</v>
+      </c>
+      <c r="K42" s="3">
         <v>900500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>754100</v>
+        <v>955400</v>
       </c>
       <c r="E43" s="3">
-        <v>679200</v>
+        <v>756200</v>
       </c>
       <c r="F43" s="3">
-        <v>507800</v>
+        <v>681200</v>
       </c>
       <c r="G43" s="3">
-        <v>440500</v>
+        <v>509200</v>
       </c>
       <c r="H43" s="3">
-        <v>436200</v>
+        <v>441800</v>
       </c>
       <c r="I43" s="3">
-        <v>390600</v>
+        <v>437400</v>
       </c>
       <c r="J43" s="3">
+        <v>391700</v>
+      </c>
+      <c r="K43" s="3">
         <v>332000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>252100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,39 +2164,42 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>333100</v>
+        <v>182800</v>
       </c>
       <c r="E45" s="3">
-        <v>266900</v>
+        <v>334000</v>
       </c>
       <c r="F45" s="3">
-        <v>163800</v>
+        <v>267700</v>
       </c>
       <c r="G45" s="3">
-        <v>73800</v>
+        <v>164300</v>
       </c>
       <c r="H45" s="3">
-        <v>41200</v>
+        <v>74000</v>
       </c>
       <c r="I45" s="3">
-        <v>31500</v>
+        <v>41300</v>
       </c>
       <c r="J45" s="3">
+        <v>31600</v>
+      </c>
+      <c r="K45" s="3">
         <v>19500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2111,39 +2209,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4721900</v>
+        <v>5723400</v>
       </c>
       <c r="E46" s="3">
-        <v>4743600</v>
+        <v>4735400</v>
       </c>
       <c r="F46" s="3">
-        <v>2567100</v>
+        <v>4757200</v>
       </c>
       <c r="G46" s="3">
-        <v>2420600</v>
+        <v>2574400</v>
       </c>
       <c r="H46" s="3">
-        <v>2436900</v>
+        <v>2427600</v>
       </c>
       <c r="I46" s="3">
-        <v>2059300</v>
+        <v>2443900</v>
       </c>
       <c r="J46" s="3">
+        <v>2065200</v>
+      </c>
+      <c r="K46" s="3">
         <v>2071300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>889100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2153,39 +2254,42 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1234700</v>
+        <v>1322000</v>
       </c>
       <c r="E47" s="3">
-        <v>993900</v>
+        <v>1238300</v>
       </c>
       <c r="F47" s="3">
-        <v>2470500</v>
+        <v>996700</v>
       </c>
       <c r="G47" s="3">
-        <v>1624200</v>
+        <v>2477600</v>
       </c>
       <c r="H47" s="3">
-        <v>1785900</v>
+        <v>1628900</v>
       </c>
       <c r="I47" s="3">
-        <v>988400</v>
+        <v>1791000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>991300</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>1000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2195,39 +2299,42 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>830000</v>
+        <v>595200</v>
       </c>
       <c r="E48" s="3">
-        <v>877800</v>
+        <v>832400</v>
       </c>
       <c r="F48" s="3">
-        <v>821300</v>
+        <v>880300</v>
       </c>
       <c r="G48" s="3">
-        <v>846300</v>
+        <v>823700</v>
       </c>
       <c r="H48" s="3">
-        <v>213700</v>
+        <v>848700</v>
       </c>
       <c r="I48" s="3">
-        <v>79200</v>
+        <v>214400</v>
       </c>
       <c r="J48" s="3">
+        <v>79400</v>
+      </c>
+      <c r="K48" s="3">
         <v>92200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>82700</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,39 +2344,42 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1405100</v>
+        <v>1328600</v>
       </c>
       <c r="E49" s="3">
-        <v>1066600</v>
+        <v>1409100</v>
       </c>
       <c r="F49" s="3">
-        <v>903800</v>
+        <v>1069600</v>
       </c>
       <c r="G49" s="3">
-        <v>581600</v>
+        <v>906400</v>
       </c>
       <c r="H49" s="3">
-        <v>188800</v>
+        <v>583200</v>
       </c>
       <c r="I49" s="3">
-        <v>175800</v>
+        <v>189300</v>
       </c>
       <c r="J49" s="3">
+        <v>176300</v>
+      </c>
+      <c r="K49" s="3">
         <v>86800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74500</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,39 +2479,42 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>93300</v>
+        <v>112100</v>
       </c>
       <c r="E52" s="3">
-        <v>97600</v>
+        <v>93600</v>
       </c>
       <c r="F52" s="3">
-        <v>100900</v>
+        <v>97900</v>
       </c>
       <c r="G52" s="3">
-        <v>84600</v>
+        <v>101200</v>
       </c>
       <c r="H52" s="3">
-        <v>79200</v>
+        <v>84900</v>
       </c>
       <c r="I52" s="3">
-        <v>68400</v>
+        <v>79400</v>
       </c>
       <c r="J52" s="3">
+        <v>68600</v>
+      </c>
+      <c r="K52" s="3">
         <v>28200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25500</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2405,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8285100</v>
+        <v>9081300</v>
       </c>
       <c r="E54" s="3">
-        <v>7779400</v>
+        <v>8308700</v>
       </c>
       <c r="F54" s="3">
-        <v>6863700</v>
+        <v>7801700</v>
       </c>
       <c r="G54" s="3">
-        <v>5557400</v>
+        <v>6883300</v>
       </c>
       <c r="H54" s="3">
-        <v>4704600</v>
+        <v>5573200</v>
       </c>
       <c r="I54" s="3">
-        <v>3371100</v>
+        <v>4718000</v>
       </c>
       <c r="J54" s="3">
+        <v>3380700</v>
+      </c>
+      <c r="K54" s="3">
         <v>2278500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1072900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>535200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>446200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,38 +2655,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>638000</v>
+        <v>720300</v>
       </c>
       <c r="E57" s="3">
-        <v>579400</v>
+        <v>639800</v>
       </c>
       <c r="F57" s="3">
-        <v>470900</v>
+        <v>581000</v>
       </c>
       <c r="G57" s="3">
-        <v>409000</v>
+        <v>472200</v>
       </c>
       <c r="H57" s="3">
-        <v>320100</v>
+        <v>410200</v>
       </c>
       <c r="I57" s="3">
-        <v>262600</v>
+        <v>321000</v>
       </c>
       <c r="J57" s="3">
+        <v>263300</v>
+      </c>
+      <c r="K57" s="3">
         <v>150800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>77600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,9 +2697,12 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2582,24 +2715,24 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3">
         <v>7600</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6100</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,39 +2742,42 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3176900</v>
+        <v>3730000</v>
       </c>
       <c r="E59" s="3">
-        <v>2920800</v>
+        <v>3186000</v>
       </c>
       <c r="F59" s="3">
-        <v>2675600</v>
+        <v>2929200</v>
       </c>
       <c r="G59" s="3">
-        <v>2229700</v>
+        <v>2683300</v>
       </c>
       <c r="H59" s="3">
-        <v>2009400</v>
+        <v>2236000</v>
       </c>
       <c r="I59" s="3">
-        <v>1754400</v>
+        <v>2015200</v>
       </c>
       <c r="J59" s="3">
+        <v>1759500</v>
+      </c>
+      <c r="K59" s="3">
         <v>1167500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>730900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2651,39 +2787,42 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3814900</v>
+        <v>4450300</v>
       </c>
       <c r="E60" s="3">
-        <v>3500200</v>
+        <v>3825800</v>
       </c>
       <c r="F60" s="3">
-        <v>3146500</v>
+        <v>3510200</v>
       </c>
       <c r="G60" s="3">
-        <v>2646300</v>
+        <v>3155500</v>
       </c>
       <c r="H60" s="3">
-        <v>2329500</v>
+        <v>2653900</v>
       </c>
       <c r="I60" s="3">
-        <v>2018100</v>
+        <v>2336200</v>
       </c>
       <c r="J60" s="3">
+        <v>2023900</v>
+      </c>
+      <c r="K60" s="3">
         <v>1323700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>814600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,39 +2832,42 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1826100</v>
+        <v>1845400</v>
       </c>
       <c r="E61" s="3">
-        <v>1932400</v>
+        <v>1831300</v>
       </c>
       <c r="F61" s="3">
-        <v>626000</v>
+        <v>1937900</v>
       </c>
       <c r="G61" s="3">
-        <v>674900</v>
+        <v>627800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>676800</v>
       </c>
       <c r="I61" s="3">
-        <v>1024200</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>1027200</v>
+      </c>
+      <c r="K61" s="3">
         <v>1201100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2735,39 +2877,42 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>39100</v>
+        <v>40300</v>
       </c>
       <c r="E62" s="3">
-        <v>47700</v>
+        <v>39200</v>
       </c>
       <c r="F62" s="3">
-        <v>47700</v>
+        <v>47900</v>
       </c>
       <c r="G62" s="3">
-        <v>26000</v>
+        <v>47900</v>
       </c>
       <c r="H62" s="3">
-        <v>103100</v>
+        <v>26100</v>
       </c>
       <c r="I62" s="3">
-        <v>70500</v>
+        <v>103400</v>
       </c>
       <c r="J62" s="3">
+        <v>70700</v>
+      </c>
+      <c r="K62" s="3">
         <v>14100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19400</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,39 +3057,42 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5680000</v>
+        <v>6336000</v>
       </c>
       <c r="E66" s="3">
-        <v>5480300</v>
+        <v>5696200</v>
       </c>
       <c r="F66" s="3">
-        <v>3820300</v>
+        <v>5496000</v>
       </c>
       <c r="G66" s="3">
-        <v>3347200</v>
+        <v>3831200</v>
       </c>
       <c r="H66" s="3">
-        <v>2432600</v>
+        <v>3356800</v>
       </c>
       <c r="I66" s="3">
-        <v>3112900</v>
+        <v>2439500</v>
       </c>
       <c r="J66" s="3">
+        <v>3121800</v>
+      </c>
+      <c r="K66" s="3">
         <v>2538900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>839100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2945,9 +3102,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,39 +3301,42 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-3957000</v>
+        <v>-4550400</v>
       </c>
       <c r="E72" s="3">
-        <v>-3493700</v>
+        <v>-3968300</v>
       </c>
       <c r="F72" s="3">
-        <v>-3569700</v>
+        <v>-3503700</v>
       </c>
       <c r="G72" s="3">
-        <v>-2939300</v>
+        <v>-3579800</v>
       </c>
       <c r="H72" s="3">
-        <v>-2717900</v>
+        <v>-2947700</v>
       </c>
       <c r="I72" s="3">
-        <v>-2633300</v>
+        <v>-2725700</v>
       </c>
       <c r="J72" s="3">
+        <v>-2640800</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1293300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-666600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,9 +3346,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2605100</v>
+        <v>2745300</v>
       </c>
       <c r="E76" s="3">
-        <v>2299100</v>
+        <v>2612500</v>
       </c>
       <c r="F76" s="3">
-        <v>3043400</v>
+        <v>2305700</v>
       </c>
       <c r="G76" s="3">
-        <v>2210100</v>
+        <v>3052100</v>
       </c>
       <c r="H76" s="3">
-        <v>2272000</v>
+        <v>2216500</v>
       </c>
       <c r="I76" s="3">
-        <v>258200</v>
+        <v>2278500</v>
       </c>
       <c r="J76" s="3">
+        <v>259000</v>
+      </c>
+      <c r="K76" s="3">
         <v>-260400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>233800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-466600</v>
+        <v>-578900</v>
       </c>
       <c r="E81" s="3">
-        <v>-36900</v>
+        <v>-467900</v>
       </c>
       <c r="F81" s="3">
-        <v>-630400</v>
+        <v>-37000</v>
       </c>
       <c r="G81" s="3">
-        <v>-201800</v>
+        <v>-632200</v>
       </c>
       <c r="H81" s="3">
-        <v>-84600</v>
+        <v>-202400</v>
       </c>
       <c r="I81" s="3">
-        <v>-1340000</v>
+        <v>-84900</v>
       </c>
       <c r="J81" s="3">
+        <v>-1343800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-584800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-234800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-212300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-75400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,38 +3688,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>185500</v>
+        <v>171900</v>
       </c>
       <c r="E83" s="3">
-        <v>137800</v>
+        <v>186100</v>
       </c>
       <c r="F83" s="3">
-        <v>120400</v>
+        <v>138200</v>
       </c>
       <c r="G83" s="3">
-        <v>94400</v>
+        <v>120800</v>
       </c>
       <c r="H83" s="3">
-        <v>34700</v>
+        <v>94700</v>
       </c>
       <c r="I83" s="3">
-        <v>58600</v>
+        <v>34800</v>
       </c>
       <c r="J83" s="3">
+        <v>58800</v>
+      </c>
+      <c r="K83" s="3">
         <v>41200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,9 +3730,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>49900</v>
+        <v>739900</v>
       </c>
       <c r="E89" s="3">
-        <v>391700</v>
+        <v>50100</v>
       </c>
       <c r="F89" s="3">
-        <v>281000</v>
+        <v>392800</v>
       </c>
       <c r="G89" s="3">
-        <v>621700</v>
+        <v>281800</v>
       </c>
       <c r="H89" s="3">
-        <v>373200</v>
+        <v>623500</v>
       </c>
       <c r="I89" s="3">
-        <v>194200</v>
+        <v>374300</v>
       </c>
       <c r="J89" s="3">
+        <v>194800</v>
+      </c>
+      <c r="K89" s="3">
         <v>109600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-38800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-83600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-29900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-27100</v>
+        <v>-6500</v>
       </c>
       <c r="E91" s="3">
-        <v>-92200</v>
+        <v>-27200</v>
       </c>
       <c r="F91" s="3">
-        <v>-84600</v>
+        <v>-92500</v>
       </c>
       <c r="G91" s="3">
-        <v>-146500</v>
+        <v>-84900</v>
       </c>
       <c r="H91" s="3">
-        <v>-135600</v>
+        <v>-146900</v>
       </c>
       <c r="I91" s="3">
-        <v>-39100</v>
+        <v>-136000</v>
       </c>
       <c r="J91" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-29300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-44900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40700</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-459000</v>
+        <v>-236100</v>
       </c>
       <c r="E94" s="3">
-        <v>-202900</v>
+        <v>-460300</v>
       </c>
       <c r="F94" s="3">
-        <v>-403600</v>
+        <v>-203500</v>
       </c>
       <c r="G94" s="3">
-        <v>-236500</v>
+        <v>-404800</v>
       </c>
       <c r="H94" s="3">
+        <v>-237200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-23900</v>
       </c>
-      <c r="I94" s="3">
-        <v>-472000</v>
-      </c>
       <c r="J94" s="3">
+        <v>-473300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-897300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,81 +4398,87 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-43400</v>
+        <v>254600</v>
       </c>
       <c r="E100" s="3">
-        <v>1356300</v>
+        <v>-43500</v>
       </c>
       <c r="F100" s="3">
-        <v>309200</v>
+        <v>1360100</v>
       </c>
       <c r="G100" s="3">
-        <v>-220300</v>
+        <v>310100</v>
       </c>
       <c r="H100" s="3">
-        <v>99800</v>
+        <v>-220900</v>
       </c>
       <c r="I100" s="3">
-        <v>36900</v>
+        <v>100100</v>
       </c>
       <c r="J100" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K100" s="3">
         <v>993900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>485900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>73400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>147100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>169300</v>
+        <v>-71800</v>
       </c>
       <c r="E101" s="3">
-        <v>183400</v>
+        <v>169700</v>
       </c>
       <c r="F101" s="3">
-        <v>-93300</v>
+        <v>183900</v>
       </c>
       <c r="G101" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="H101" s="3">
         <v>23900</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
-        <v>-60800</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-34700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>20400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-283200</v>
+        <v>686600</v>
       </c>
       <c r="E102" s="3">
-        <v>1728400</v>
+        <v>-284000</v>
       </c>
       <c r="F102" s="3">
-        <v>93300</v>
+        <v>1733300</v>
       </c>
       <c r="G102" s="3">
-        <v>188800</v>
+        <v>93600</v>
       </c>
       <c r="H102" s="3">
-        <v>449200</v>
+        <v>189300</v>
       </c>
       <c r="I102" s="3">
-        <v>-301600</v>
+        <v>450500</v>
       </c>
       <c r="J102" s="3">
+        <v>-302500</v>
+      </c>
+      <c r="K102" s="3">
         <v>171400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>399100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-33900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>68200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>14414100</v>
+        <v>14316000</v>
       </c>
       <c r="E8" s="3">
-        <v>12760100</v>
+        <v>12673400</v>
       </c>
       <c r="F8" s="3">
-        <v>10519800</v>
+        <v>10448200</v>
       </c>
       <c r="G8" s="3">
-        <v>8574200</v>
+        <v>8515900</v>
       </c>
       <c r="H8" s="3">
-        <v>7359900</v>
+        <v>7309900</v>
       </c>
       <c r="I8" s="3">
-        <v>5722300</v>
+        <v>5683400</v>
       </c>
       <c r="J8" s="3">
-        <v>4450300</v>
+        <v>4420100</v>
       </c>
       <c r="K8" s="3">
         <v>3202900</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10693800</v>
+        <v>10621100</v>
       </c>
       <c r="E9" s="3">
-        <v>9576400</v>
+        <v>9511200</v>
       </c>
       <c r="F9" s="3">
-        <v>7700500</v>
+        <v>7648100</v>
       </c>
       <c r="G9" s="3">
-        <v>6381700</v>
+        <v>6338300</v>
       </c>
       <c r="H9" s="3">
-        <v>5486200</v>
+        <v>5448900</v>
       </c>
       <c r="I9" s="3">
-        <v>4250100</v>
+        <v>4221200</v>
       </c>
       <c r="J9" s="3">
-        <v>3526500</v>
+        <v>3502500</v>
       </c>
       <c r="K9" s="3">
         <v>2767800</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3720200</v>
+        <v>3694900</v>
       </c>
       <c r="E10" s="3">
-        <v>3183800</v>
+        <v>3162100</v>
       </c>
       <c r="F10" s="3">
-        <v>2819300</v>
+        <v>2800100</v>
       </c>
       <c r="G10" s="3">
-        <v>2192500</v>
+        <v>2177600</v>
       </c>
       <c r="H10" s="3">
-        <v>1873700</v>
+        <v>1861000</v>
       </c>
       <c r="I10" s="3">
-        <v>1472200</v>
+        <v>1462200</v>
       </c>
       <c r="J10" s="3">
-        <v>923800</v>
+        <v>917500</v>
       </c>
       <c r="K10" s="3">
         <v>435100</v>
@@ -881,25 +881,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1665900</v>
+        <v>1654600</v>
       </c>
       <c r="E12" s="3">
-        <v>1465700</v>
+        <v>1455700</v>
       </c>
       <c r="F12" s="3">
-        <v>965100</v>
+        <v>958600</v>
       </c>
       <c r="G12" s="3">
-        <v>891200</v>
+        <v>885100</v>
       </c>
       <c r="H12" s="3">
-        <v>653900</v>
+        <v>649500</v>
       </c>
       <c r="I12" s="3">
-        <v>536400</v>
+        <v>532800</v>
       </c>
       <c r="J12" s="3">
-        <v>430900</v>
+        <v>428000</v>
       </c>
       <c r="K12" s="3">
         <v>224600</v>
@@ -971,13 +971,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>364500</v>
+        <v>362000</v>
       </c>
       <c r="E14" s="3">
         <v>2200</v>
       </c>
       <c r="F14" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="G14" s="3">
         <v>5400</v>
@@ -1019,16 +1019,16 @@
         <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>43500</v>
+        <v>43200</v>
       </c>
       <c r="F15" s="3">
-        <v>27200</v>
+        <v>27000</v>
       </c>
       <c r="G15" s="3">
-        <v>19600</v>
+        <v>19500</v>
       </c>
       <c r="H15" s="3">
-        <v>15200</v>
+        <v>15100</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14899400</v>
+        <v>14798000</v>
       </c>
       <c r="E17" s="3">
-        <v>13477200</v>
+        <v>13385600</v>
       </c>
       <c r="F17" s="3">
-        <v>10417500</v>
+        <v>10346600</v>
       </c>
       <c r="G17" s="3">
-        <v>8893000</v>
+        <v>8832600</v>
       </c>
       <c r="H17" s="3">
-        <v>7439300</v>
+        <v>7388700</v>
       </c>
       <c r="I17" s="3">
-        <v>5770200</v>
+        <v>5731000</v>
       </c>
       <c r="J17" s="3">
-        <v>4860500</v>
+        <v>4827500</v>
       </c>
       <c r="K17" s="3">
         <v>3583800</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-485300</v>
+        <v>-482000</v>
       </c>
       <c r="E18" s="3">
-        <v>-717100</v>
+        <v>-712200</v>
       </c>
       <c r="F18" s="3">
-        <v>102300</v>
+        <v>101600</v>
       </c>
       <c r="G18" s="3">
-        <v>-318800</v>
+        <v>-316600</v>
       </c>
       <c r="H18" s="3">
-        <v>-79400</v>
+        <v>-78900</v>
       </c>
       <c r="I18" s="3">
-        <v>-47900</v>
+        <v>-47600</v>
       </c>
       <c r="J18" s="3">
-        <v>-410200</v>
+        <v>-407400</v>
       </c>
       <c r="K18" s="3">
         <v>-380800</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-22900</v>
+        <v>-22700</v>
       </c>
       <c r="E20" s="3">
-        <v>359100</v>
+        <v>356600</v>
       </c>
       <c r="F20" s="3">
-        <v>212200</v>
+        <v>210700</v>
       </c>
       <c r="G20" s="3">
-        <v>-408000</v>
+        <v>-405300</v>
       </c>
       <c r="H20" s="3">
-        <v>-21800</v>
+        <v>-21600</v>
       </c>
       <c r="I20" s="3">
-        <v>-140400</v>
+        <v>-139400</v>
       </c>
       <c r="J20" s="3">
-        <v>-927100</v>
+        <v>-920800</v>
       </c>
       <c r="K20" s="3">
         <v>-199600</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-335200</v>
+        <v>-335000</v>
       </c>
       <c r="E21" s="3">
-        <v>-170800</v>
+        <v>-171900</v>
       </c>
       <c r="F21" s="3">
-        <v>453500</v>
+        <v>448700</v>
       </c>
       <c r="G21" s="3">
-        <v>-605400</v>
+        <v>-602700</v>
       </c>
       <c r="H21" s="3">
-        <v>-6000</v>
+        <v>-7100</v>
       </c>
       <c r="I21" s="3">
-        <v>-153200</v>
+        <v>-152600</v>
       </c>
       <c r="J21" s="3">
-        <v>-1278200</v>
+        <v>-1270200</v>
       </c>
       <c r="K21" s="3">
         <v>-539300</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>41300</v>
+        <v>41100</v>
       </c>
       <c r="E22" s="3">
-        <v>44600</v>
+        <v>44300</v>
       </c>
       <c r="F22" s="3">
-        <v>43500</v>
+        <v>43200</v>
       </c>
       <c r="G22" s="3">
-        <v>44600</v>
+        <v>44300</v>
       </c>
       <c r="H22" s="3">
-        <v>41300</v>
+        <v>41100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="3">
-        <v>4400</v>
+        <v>4300</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-549500</v>
+        <v>-545800</v>
       </c>
       <c r="E23" s="3">
-        <v>-402600</v>
+        <v>-399900</v>
       </c>
       <c r="F23" s="3">
-        <v>270900</v>
+        <v>269100</v>
       </c>
       <c r="G23" s="3">
-        <v>-771500</v>
+        <v>-766200</v>
       </c>
       <c r="H23" s="3">
-        <v>-142500</v>
+        <v>-141600</v>
       </c>
       <c r="I23" s="3">
-        <v>-188200</v>
+        <v>-187000</v>
       </c>
       <c r="J23" s="3">
-        <v>-1341600</v>
+        <v>-1332500</v>
       </c>
       <c r="K23" s="3">
         <v>-580500</v>
@@ -1366,22 +1366,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>29400</v>
+        <v>29200</v>
       </c>
       <c r="E24" s="3">
-        <v>65300</v>
+        <v>64800</v>
       </c>
       <c r="F24" s="3">
-        <v>307900</v>
+        <v>305800</v>
       </c>
       <c r="G24" s="3">
-        <v>-139300</v>
+        <v>-138300</v>
       </c>
       <c r="H24" s="3">
-        <v>59800</v>
+        <v>59400</v>
       </c>
       <c r="I24" s="3">
-        <v>-103400</v>
+        <v>-102700</v>
       </c>
       <c r="J24" s="3">
         <v>2200</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-578900</v>
+        <v>-574900</v>
       </c>
       <c r="E26" s="3">
-        <v>-467900</v>
+        <v>-464700</v>
       </c>
       <c r="F26" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="G26" s="3">
-        <v>-632200</v>
+        <v>-627900</v>
       </c>
       <c r="H26" s="3">
-        <v>-202400</v>
+        <v>-201000</v>
       </c>
       <c r="I26" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="J26" s="3">
-        <v>-1343800</v>
+        <v>-1334700</v>
       </c>
       <c r="K26" s="3">
         <v>-584800</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-578900</v>
+        <v>-574900</v>
       </c>
       <c r="E27" s="3">
-        <v>-467900</v>
+        <v>-464700</v>
       </c>
       <c r="F27" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="G27" s="3">
-        <v>-632200</v>
+        <v>-627900</v>
       </c>
       <c r="H27" s="3">
-        <v>-202400</v>
+        <v>-201000</v>
       </c>
       <c r="I27" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="J27" s="3">
-        <v>-1343800</v>
+        <v>-1334700</v>
       </c>
       <c r="K27" s="3">
         <v>-584800</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>22900</v>
+        <v>22700</v>
       </c>
       <c r="E32" s="3">
-        <v>-359100</v>
+        <v>-356600</v>
       </c>
       <c r="F32" s="3">
-        <v>-212200</v>
+        <v>-210700</v>
       </c>
       <c r="G32" s="3">
-        <v>408000</v>
+        <v>405300</v>
       </c>
       <c r="H32" s="3">
-        <v>21800</v>
+        <v>21600</v>
       </c>
       <c r="I32" s="3">
-        <v>140400</v>
+        <v>139400</v>
       </c>
       <c r="J32" s="3">
-        <v>927100</v>
+        <v>920800</v>
       </c>
       <c r="K32" s="3">
         <v>199600</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-578900</v>
+        <v>-574900</v>
       </c>
       <c r="E33" s="3">
-        <v>-467900</v>
+        <v>-464700</v>
       </c>
       <c r="F33" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="G33" s="3">
-        <v>-632200</v>
+        <v>-627900</v>
       </c>
       <c r="H33" s="3">
-        <v>-202400</v>
+        <v>-201000</v>
       </c>
       <c r="I33" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="J33" s="3">
-        <v>-1343800</v>
+        <v>-1334700</v>
       </c>
       <c r="K33" s="3">
         <v>-584800</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-578900</v>
+        <v>-574900</v>
       </c>
       <c r="E35" s="3">
-        <v>-467900</v>
+        <v>-464700</v>
       </c>
       <c r="F35" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="G35" s="3">
-        <v>-632200</v>
+        <v>-627900</v>
       </c>
       <c r="H35" s="3">
-        <v>-202400</v>
+        <v>-201000</v>
       </c>
       <c r="I35" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="J35" s="3">
-        <v>-1343800</v>
+        <v>-1334700</v>
       </c>
       <c r="K35" s="3">
         <v>-584800</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3388300</v>
+        <v>3365300</v>
       </c>
       <c r="E41" s="3">
-        <v>2701800</v>
+        <v>2683400</v>
       </c>
       <c r="F41" s="3">
-        <v>2985700</v>
+        <v>2965400</v>
       </c>
       <c r="G41" s="3">
-        <v>1252400</v>
+        <v>1243900</v>
       </c>
       <c r="H41" s="3">
-        <v>1158800</v>
+        <v>1150900</v>
       </c>
       <c r="I41" s="3">
-        <v>969500</v>
+        <v>962900</v>
       </c>
       <c r="J41" s="3">
-        <v>519000</v>
+        <v>515500</v>
       </c>
       <c r="K41" s="3">
         <v>819200</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1196900</v>
+        <v>1188800</v>
       </c>
       <c r="E42" s="3">
-        <v>943400</v>
+        <v>937000</v>
       </c>
       <c r="F42" s="3">
-        <v>822600</v>
+        <v>817000</v>
       </c>
       <c r="G42" s="3">
-        <v>648500</v>
+        <v>644100</v>
       </c>
       <c r="H42" s="3">
-        <v>753000</v>
+        <v>747800</v>
       </c>
       <c r="I42" s="3">
-        <v>995600</v>
+        <v>988800</v>
       </c>
       <c r="J42" s="3">
-        <v>1122900</v>
+        <v>1115300</v>
       </c>
       <c r="K42" s="3">
         <v>900500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>955400</v>
+        <v>948900</v>
       </c>
       <c r="E43" s="3">
-        <v>756200</v>
+        <v>751100</v>
       </c>
       <c r="F43" s="3">
-        <v>681200</v>
+        <v>676500</v>
       </c>
       <c r="G43" s="3">
-        <v>509200</v>
+        <v>505800</v>
       </c>
       <c r="H43" s="3">
-        <v>441800</v>
+        <v>438800</v>
       </c>
       <c r="I43" s="3">
-        <v>437400</v>
+        <v>434400</v>
       </c>
       <c r="J43" s="3">
-        <v>391700</v>
+        <v>389100</v>
       </c>
       <c r="K43" s="3">
         <v>332000</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>182800</v>
+        <v>181600</v>
       </c>
       <c r="E45" s="3">
-        <v>334000</v>
+        <v>331800</v>
       </c>
       <c r="F45" s="3">
-        <v>267700</v>
+        <v>265900</v>
       </c>
       <c r="G45" s="3">
-        <v>164300</v>
+        <v>163200</v>
       </c>
       <c r="H45" s="3">
-        <v>74000</v>
+        <v>73500</v>
       </c>
       <c r="I45" s="3">
-        <v>41300</v>
+        <v>41100</v>
       </c>
       <c r="J45" s="3">
-        <v>31600</v>
+        <v>31300</v>
       </c>
       <c r="K45" s="3">
         <v>19500</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5723400</v>
+        <v>5684500</v>
       </c>
       <c r="E46" s="3">
-        <v>4735400</v>
+        <v>4703200</v>
       </c>
       <c r="F46" s="3">
-        <v>4757200</v>
+        <v>4724800</v>
       </c>
       <c r="G46" s="3">
-        <v>2574400</v>
+        <v>2556900</v>
       </c>
       <c r="H46" s="3">
-        <v>2427600</v>
+        <v>2411000</v>
       </c>
       <c r="I46" s="3">
-        <v>2443900</v>
+        <v>2427300</v>
       </c>
       <c r="J46" s="3">
-        <v>2065200</v>
+        <v>2051200</v>
       </c>
       <c r="K46" s="3">
         <v>2071300</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1322000</v>
+        <v>1313100</v>
       </c>
       <c r="E47" s="3">
-        <v>1238300</v>
+        <v>1229800</v>
       </c>
       <c r="F47" s="3">
-        <v>996700</v>
+        <v>989900</v>
       </c>
       <c r="G47" s="3">
-        <v>2477600</v>
+        <v>2460800</v>
       </c>
       <c r="H47" s="3">
-        <v>1628900</v>
+        <v>1617800</v>
       </c>
       <c r="I47" s="3">
-        <v>1791000</v>
+        <v>1778800</v>
       </c>
       <c r="J47" s="3">
-        <v>991300</v>
+        <v>984500</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>595200</v>
+        <v>591100</v>
       </c>
       <c r="E48" s="3">
-        <v>832400</v>
+        <v>826700</v>
       </c>
       <c r="F48" s="3">
-        <v>880300</v>
+        <v>874300</v>
       </c>
       <c r="G48" s="3">
-        <v>823700</v>
+        <v>818100</v>
       </c>
       <c r="H48" s="3">
-        <v>848700</v>
+        <v>842900</v>
       </c>
       <c r="I48" s="3">
-        <v>214400</v>
+        <v>212900</v>
       </c>
       <c r="J48" s="3">
-        <v>79400</v>
+        <v>78900</v>
       </c>
       <c r="K48" s="3">
         <v>92200</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1328600</v>
+        <v>1319500</v>
       </c>
       <c r="E49" s="3">
-        <v>1409100</v>
+        <v>1399500</v>
       </c>
       <c r="F49" s="3">
-        <v>1069600</v>
+        <v>1062300</v>
       </c>
       <c r="G49" s="3">
-        <v>906400</v>
+        <v>900200</v>
       </c>
       <c r="H49" s="3">
-        <v>583200</v>
+        <v>579300</v>
       </c>
       <c r="I49" s="3">
-        <v>189300</v>
+        <v>188000</v>
       </c>
       <c r="J49" s="3">
-        <v>176300</v>
+        <v>175100</v>
       </c>
       <c r="K49" s="3">
         <v>86800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>112100</v>
+        <v>111300</v>
       </c>
       <c r="E52" s="3">
-        <v>93600</v>
+        <v>92900</v>
       </c>
       <c r="F52" s="3">
-        <v>97900</v>
+        <v>97300</v>
       </c>
       <c r="G52" s="3">
-        <v>101200</v>
+        <v>100500</v>
       </c>
       <c r="H52" s="3">
-        <v>84900</v>
+        <v>84300</v>
       </c>
       <c r="I52" s="3">
-        <v>79400</v>
+        <v>78900</v>
       </c>
       <c r="J52" s="3">
-        <v>68600</v>
+        <v>68100</v>
       </c>
       <c r="K52" s="3">
         <v>28200</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9081300</v>
+        <v>9019500</v>
       </c>
       <c r="E54" s="3">
-        <v>8308700</v>
+        <v>8252200</v>
       </c>
       <c r="F54" s="3">
-        <v>7801700</v>
+        <v>7748600</v>
       </c>
       <c r="G54" s="3">
-        <v>6883300</v>
+        <v>6836500</v>
       </c>
       <c r="H54" s="3">
-        <v>5573200</v>
+        <v>5535300</v>
       </c>
       <c r="I54" s="3">
-        <v>4718000</v>
+        <v>4685900</v>
       </c>
       <c r="J54" s="3">
-        <v>3380700</v>
+        <v>3357700</v>
       </c>
       <c r="K54" s="3">
         <v>2278500</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>720300</v>
+        <v>715400</v>
       </c>
       <c r="E57" s="3">
-        <v>639800</v>
+        <v>635500</v>
       </c>
       <c r="F57" s="3">
-        <v>581000</v>
+        <v>577100</v>
       </c>
       <c r="G57" s="3">
-        <v>472200</v>
+        <v>469000</v>
       </c>
       <c r="H57" s="3">
-        <v>410200</v>
+        <v>407400</v>
       </c>
       <c r="I57" s="3">
-        <v>321000</v>
+        <v>318800</v>
       </c>
       <c r="J57" s="3">
-        <v>263300</v>
+        <v>261500</v>
       </c>
       <c r="K57" s="3">
         <v>150800</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3730000</v>
+        <v>3704600</v>
       </c>
       <c r="E59" s="3">
-        <v>3186000</v>
+        <v>3164300</v>
       </c>
       <c r="F59" s="3">
-        <v>2929200</v>
+        <v>2909200</v>
       </c>
       <c r="G59" s="3">
-        <v>2683300</v>
+        <v>2665000</v>
       </c>
       <c r="H59" s="3">
-        <v>2236000</v>
+        <v>2220800</v>
       </c>
       <c r="I59" s="3">
-        <v>2015200</v>
+        <v>2001500</v>
       </c>
       <c r="J59" s="3">
-        <v>1759500</v>
+        <v>1747500</v>
       </c>
       <c r="K59" s="3">
         <v>1167500</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4450300</v>
+        <v>4420100</v>
       </c>
       <c r="E60" s="3">
-        <v>3825800</v>
+        <v>3799700</v>
       </c>
       <c r="F60" s="3">
-        <v>3510200</v>
+        <v>3486300</v>
       </c>
       <c r="G60" s="3">
-        <v>3155500</v>
+        <v>3134000</v>
       </c>
       <c r="H60" s="3">
-        <v>2653900</v>
+        <v>2635800</v>
       </c>
       <c r="I60" s="3">
-        <v>2336200</v>
+        <v>2320300</v>
       </c>
       <c r="J60" s="3">
-        <v>2023900</v>
+        <v>2010100</v>
       </c>
       <c r="K60" s="3">
         <v>1323700</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1845400</v>
+        <v>1832900</v>
       </c>
       <c r="E61" s="3">
-        <v>1831300</v>
+        <v>1818800</v>
       </c>
       <c r="F61" s="3">
-        <v>1937900</v>
+        <v>1924700</v>
       </c>
       <c r="G61" s="3">
-        <v>627800</v>
+        <v>623600</v>
       </c>
       <c r="H61" s="3">
-        <v>676800</v>
+        <v>672200</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>1027200</v>
+        <v>1020200</v>
       </c>
       <c r="K61" s="3">
         <v>1201100</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>40300</v>
+        <v>40000</v>
       </c>
       <c r="E62" s="3">
-        <v>39200</v>
+        <v>38900</v>
       </c>
       <c r="F62" s="3">
-        <v>47900</v>
+        <v>47600</v>
       </c>
       <c r="G62" s="3">
-        <v>47900</v>
+        <v>47600</v>
       </c>
       <c r="H62" s="3">
-        <v>26100</v>
+        <v>25900</v>
       </c>
       <c r="I62" s="3">
-        <v>103400</v>
+        <v>102700</v>
       </c>
       <c r="J62" s="3">
-        <v>70700</v>
+        <v>70200</v>
       </c>
       <c r="K62" s="3">
         <v>14100</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6336000</v>
+        <v>6292900</v>
       </c>
       <c r="E66" s="3">
-        <v>5696200</v>
+        <v>5657500</v>
       </c>
       <c r="F66" s="3">
-        <v>5496000</v>
+        <v>5458600</v>
       </c>
       <c r="G66" s="3">
-        <v>3831200</v>
+        <v>3805100</v>
       </c>
       <c r="H66" s="3">
-        <v>3356800</v>
+        <v>3334000</v>
       </c>
       <c r="I66" s="3">
-        <v>2439500</v>
+        <v>2422900</v>
       </c>
       <c r="J66" s="3">
-        <v>3121800</v>
+        <v>3100500</v>
       </c>
       <c r="K66" s="3">
         <v>2538900</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-4550400</v>
+        <v>-4519500</v>
       </c>
       <c r="E72" s="3">
-        <v>-3968300</v>
+        <v>-3941300</v>
       </c>
       <c r="F72" s="3">
-        <v>-3503700</v>
+        <v>-3479900</v>
       </c>
       <c r="G72" s="3">
-        <v>-3579800</v>
+        <v>-3555500</v>
       </c>
       <c r="H72" s="3">
-        <v>-2947700</v>
+        <v>-2927600</v>
       </c>
       <c r="I72" s="3">
-        <v>-2725700</v>
+        <v>-2707200</v>
       </c>
       <c r="J72" s="3">
-        <v>-2640800</v>
+        <v>-2622900</v>
       </c>
       <c r="K72" s="3">
         <v>-1293300</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2745300</v>
+        <v>2726600</v>
       </c>
       <c r="E76" s="3">
-        <v>2612500</v>
+        <v>2594800</v>
       </c>
       <c r="F76" s="3">
-        <v>2305700</v>
+        <v>2290000</v>
       </c>
       <c r="G76" s="3">
-        <v>3052100</v>
+        <v>3031400</v>
       </c>
       <c r="H76" s="3">
-        <v>2216500</v>
+        <v>2201400</v>
       </c>
       <c r="I76" s="3">
-        <v>2278500</v>
+        <v>2263000</v>
       </c>
       <c r="J76" s="3">
-        <v>259000</v>
+        <v>257200</v>
       </c>
       <c r="K76" s="3">
         <v>-260400</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-578900</v>
+        <v>-574900</v>
       </c>
       <c r="E81" s="3">
-        <v>-467900</v>
+        <v>-464700</v>
       </c>
       <c r="F81" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="G81" s="3">
-        <v>-632200</v>
+        <v>-627900</v>
       </c>
       <c r="H81" s="3">
-        <v>-202400</v>
+        <v>-201000</v>
       </c>
       <c r="I81" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="J81" s="3">
-        <v>-1343800</v>
+        <v>-1334700</v>
       </c>
       <c r="K81" s="3">
         <v>-584800</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>171900</v>
+        <v>170800</v>
       </c>
       <c r="E83" s="3">
-        <v>186100</v>
+        <v>184800</v>
       </c>
       <c r="F83" s="3">
-        <v>138200</v>
+        <v>137200</v>
       </c>
       <c r="G83" s="3">
-        <v>120800</v>
+        <v>120000</v>
       </c>
       <c r="H83" s="3">
-        <v>94700</v>
+        <v>94000</v>
       </c>
       <c r="I83" s="3">
-        <v>34800</v>
+        <v>34600</v>
       </c>
       <c r="J83" s="3">
-        <v>58800</v>
+        <v>58400</v>
       </c>
       <c r="K83" s="3">
         <v>41200</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>739900</v>
+        <v>734900</v>
       </c>
       <c r="E89" s="3">
-        <v>50100</v>
+        <v>49700</v>
       </c>
       <c r="F89" s="3">
-        <v>392800</v>
+        <v>390100</v>
       </c>
       <c r="G89" s="3">
-        <v>281800</v>
+        <v>279900</v>
       </c>
       <c r="H89" s="3">
-        <v>623500</v>
+        <v>619200</v>
       </c>
       <c r="I89" s="3">
-        <v>374300</v>
+        <v>371800</v>
       </c>
       <c r="J89" s="3">
-        <v>194800</v>
+        <v>193400</v>
       </c>
       <c r="K89" s="3">
         <v>109600</v>
@@ -4032,22 +4032,22 @@
         <v>-6500</v>
       </c>
       <c r="E91" s="3">
-        <v>-27200</v>
+        <v>-27000</v>
       </c>
       <c r="F91" s="3">
-        <v>-92500</v>
+        <v>-91900</v>
       </c>
       <c r="G91" s="3">
-        <v>-84900</v>
+        <v>-84300</v>
       </c>
       <c r="H91" s="3">
-        <v>-146900</v>
+        <v>-145900</v>
       </c>
       <c r="I91" s="3">
-        <v>-136000</v>
+        <v>-135100</v>
       </c>
       <c r="J91" s="3">
-        <v>-39200</v>
+        <v>-38900</v>
       </c>
       <c r="K91" s="3">
         <v>-29300</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-236100</v>
+        <v>-234500</v>
       </c>
       <c r="E94" s="3">
-        <v>-460300</v>
+        <v>-457100</v>
       </c>
       <c r="F94" s="3">
-        <v>-203500</v>
+        <v>-202100</v>
       </c>
       <c r="G94" s="3">
-        <v>-404800</v>
+        <v>-402000</v>
       </c>
       <c r="H94" s="3">
-        <v>-237200</v>
+        <v>-235600</v>
       </c>
       <c r="I94" s="3">
-        <v>-23900</v>
+        <v>-23800</v>
       </c>
       <c r="J94" s="3">
-        <v>-473300</v>
+        <v>-470100</v>
       </c>
       <c r="K94" s="3">
         <v>-897300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>254600</v>
+        <v>252900</v>
       </c>
       <c r="E100" s="3">
-        <v>-43500</v>
+        <v>-43200</v>
       </c>
       <c r="F100" s="3">
-        <v>1360100</v>
+        <v>1350900</v>
       </c>
       <c r="G100" s="3">
-        <v>310100</v>
+        <v>308000</v>
       </c>
       <c r="H100" s="3">
-        <v>-220900</v>
+        <v>-219400</v>
       </c>
       <c r="I100" s="3">
-        <v>100100</v>
+        <v>99400</v>
       </c>
       <c r="J100" s="3">
-        <v>37000</v>
+        <v>36700</v>
       </c>
       <c r="K100" s="3">
         <v>993900</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-71800</v>
+        <v>-71300</v>
       </c>
       <c r="E101" s="3">
-        <v>169700</v>
+        <v>168600</v>
       </c>
       <c r="F101" s="3">
-        <v>183900</v>
+        <v>182600</v>
       </c>
       <c r="G101" s="3">
-        <v>-93600</v>
+        <v>-92900</v>
       </c>
       <c r="H101" s="3">
-        <v>23900</v>
+        <v>23800</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>-60900</v>
+        <v>-60500</v>
       </c>
       <c r="K101" s="3">
         <v>-34700</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>686600</v>
+        <v>681900</v>
       </c>
       <c r="E102" s="3">
-        <v>-284000</v>
+        <v>-282100</v>
       </c>
       <c r="F102" s="3">
-        <v>1733300</v>
+        <v>1721600</v>
       </c>
       <c r="G102" s="3">
-        <v>93600</v>
+        <v>92900</v>
       </c>
       <c r="H102" s="3">
-        <v>189300</v>
+        <v>188000</v>
       </c>
       <c r="I102" s="3">
-        <v>450500</v>
+        <v>447400</v>
       </c>
       <c r="J102" s="3">
-        <v>-302500</v>
+        <v>-300400</v>
       </c>
       <c r="K102" s="3">
         <v>171400</v>

--- a/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>14316000</v>
+        <v>14672400</v>
       </c>
       <c r="E8" s="3">
-        <v>12673400</v>
+        <v>12988800</v>
       </c>
       <c r="F8" s="3">
-        <v>10448200</v>
+        <v>10708300</v>
       </c>
       <c r="G8" s="3">
-        <v>8515900</v>
+        <v>8727900</v>
       </c>
       <c r="H8" s="3">
-        <v>7309900</v>
+        <v>7491800</v>
       </c>
       <c r="I8" s="3">
-        <v>5683400</v>
+        <v>5824900</v>
       </c>
       <c r="J8" s="3">
-        <v>4420100</v>
+        <v>4530100</v>
       </c>
       <c r="K8" s="3">
         <v>3202900</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10621100</v>
+        <v>10885500</v>
       </c>
       <c r="E9" s="3">
-        <v>9511200</v>
+        <v>9748000</v>
       </c>
       <c r="F9" s="3">
-        <v>7648100</v>
+        <v>7838500</v>
       </c>
       <c r="G9" s="3">
-        <v>6338300</v>
+        <v>6496100</v>
       </c>
       <c r="H9" s="3">
-        <v>5448900</v>
+        <v>5584500</v>
       </c>
       <c r="I9" s="3">
-        <v>4221200</v>
+        <v>4326300</v>
       </c>
       <c r="J9" s="3">
-        <v>3502500</v>
+        <v>3589700</v>
       </c>
       <c r="K9" s="3">
         <v>2767800</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3694900</v>
+        <v>3786900</v>
       </c>
       <c r="E10" s="3">
-        <v>3162100</v>
+        <v>3240800</v>
       </c>
       <c r="F10" s="3">
-        <v>2800100</v>
+        <v>2869800</v>
       </c>
       <c r="G10" s="3">
-        <v>2177600</v>
+        <v>2231800</v>
       </c>
       <c r="H10" s="3">
-        <v>1861000</v>
+        <v>1907300</v>
       </c>
       <c r="I10" s="3">
-        <v>1462200</v>
+        <v>1498600</v>
       </c>
       <c r="J10" s="3">
-        <v>917500</v>
+        <v>940400</v>
       </c>
       <c r="K10" s="3">
         <v>435100</v>
@@ -881,25 +881,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1654600</v>
+        <v>1695700</v>
       </c>
       <c r="E12" s="3">
-        <v>1455700</v>
+        <v>1491900</v>
       </c>
       <c r="F12" s="3">
-        <v>958600</v>
+        <v>982400</v>
       </c>
       <c r="G12" s="3">
-        <v>885100</v>
+        <v>907100</v>
       </c>
       <c r="H12" s="3">
-        <v>649500</v>
+        <v>665700</v>
       </c>
       <c r="I12" s="3">
-        <v>532800</v>
+        <v>546000</v>
       </c>
       <c r="J12" s="3">
-        <v>428000</v>
+        <v>438600</v>
       </c>
       <c r="K12" s="3">
         <v>224600</v>
@@ -971,16 +971,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>362000</v>
+        <v>371000</v>
       </c>
       <c r="E14" s="3">
         <v>2200</v>
       </c>
       <c r="F14" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G14" s="3">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1019,16 +1019,16 @@
         <v>3</v>
       </c>
       <c r="E15" s="3">
-        <v>43200</v>
+        <v>44300</v>
       </c>
       <c r="F15" s="3">
-        <v>27000</v>
+        <v>27700</v>
       </c>
       <c r="G15" s="3">
-        <v>19500</v>
+        <v>19900</v>
       </c>
       <c r="H15" s="3">
-        <v>15100</v>
+        <v>15500</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>3</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14798000</v>
+        <v>15166400</v>
       </c>
       <c r="E17" s="3">
-        <v>13385600</v>
+        <v>13718700</v>
       </c>
       <c r="F17" s="3">
-        <v>10346600</v>
+        <v>10604200</v>
       </c>
       <c r="G17" s="3">
-        <v>8832600</v>
+        <v>9052400</v>
       </c>
       <c r="H17" s="3">
-        <v>7388700</v>
+        <v>7572700</v>
       </c>
       <c r="I17" s="3">
-        <v>5731000</v>
+        <v>5873600</v>
       </c>
       <c r="J17" s="3">
-        <v>4827500</v>
+        <v>4947600</v>
       </c>
       <c r="K17" s="3">
         <v>3583800</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-482000</v>
+        <v>-494000</v>
       </c>
       <c r="E18" s="3">
-        <v>-712200</v>
+        <v>-729900</v>
       </c>
       <c r="F18" s="3">
-        <v>101600</v>
+        <v>104100</v>
       </c>
       <c r="G18" s="3">
-        <v>-316600</v>
+        <v>-324500</v>
       </c>
       <c r="H18" s="3">
-        <v>-78900</v>
+        <v>-80900</v>
       </c>
       <c r="I18" s="3">
-        <v>-47600</v>
+        <v>-48700</v>
       </c>
       <c r="J18" s="3">
-        <v>-407400</v>
+        <v>-417600</v>
       </c>
       <c r="K18" s="3">
         <v>-380800</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-22700</v>
+        <v>-23300</v>
       </c>
       <c r="E20" s="3">
-        <v>356600</v>
+        <v>365500</v>
       </c>
       <c r="F20" s="3">
-        <v>210700</v>
+        <v>216000</v>
       </c>
       <c r="G20" s="3">
-        <v>-405300</v>
+        <v>-415400</v>
       </c>
       <c r="H20" s="3">
-        <v>-21600</v>
+        <v>-22200</v>
       </c>
       <c r="I20" s="3">
-        <v>-139400</v>
+        <v>-142900</v>
       </c>
       <c r="J20" s="3">
-        <v>-920800</v>
+        <v>-943700</v>
       </c>
       <c r="K20" s="3">
         <v>-199600</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-335000</v>
+        <v>-342300</v>
       </c>
       <c r="E21" s="3">
-        <v>-171900</v>
+        <v>-175000</v>
       </c>
       <c r="F21" s="3">
-        <v>448700</v>
+        <v>460700</v>
       </c>
       <c r="G21" s="3">
-        <v>-602700</v>
+        <v>-617000</v>
       </c>
       <c r="H21" s="3">
-        <v>-7100</v>
+        <v>-6700</v>
       </c>
       <c r="I21" s="3">
-        <v>-152600</v>
+        <v>-156200</v>
       </c>
       <c r="J21" s="3">
-        <v>-1270200</v>
+        <v>-1301400</v>
       </c>
       <c r="K21" s="3">
         <v>-539300</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="E22" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F22" s="3">
         <v>44300</v>
       </c>
-      <c r="F22" s="3">
-        <v>43200</v>
-      </c>
       <c r="G22" s="3">
-        <v>44300</v>
+        <v>45400</v>
       </c>
       <c r="H22" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J22" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-545800</v>
+        <v>-559300</v>
       </c>
       <c r="E23" s="3">
-        <v>-399900</v>
+        <v>-409800</v>
       </c>
       <c r="F23" s="3">
-        <v>269100</v>
+        <v>275800</v>
       </c>
       <c r="G23" s="3">
-        <v>-766200</v>
+        <v>-785300</v>
       </c>
       <c r="H23" s="3">
-        <v>-141600</v>
+        <v>-145100</v>
       </c>
       <c r="I23" s="3">
-        <v>-187000</v>
+        <v>-191600</v>
       </c>
       <c r="J23" s="3">
-        <v>-1332500</v>
+        <v>-1365700</v>
       </c>
       <c r="K23" s="3">
         <v>-580500</v>
@@ -1366,22 +1366,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>29200</v>
+        <v>29900</v>
       </c>
       <c r="E24" s="3">
-        <v>64800</v>
+        <v>66500</v>
       </c>
       <c r="F24" s="3">
-        <v>305800</v>
+        <v>313500</v>
       </c>
       <c r="G24" s="3">
-        <v>-138300</v>
+        <v>-141800</v>
       </c>
       <c r="H24" s="3">
-        <v>59400</v>
+        <v>60900</v>
       </c>
       <c r="I24" s="3">
-        <v>-102700</v>
+        <v>-105200</v>
       </c>
       <c r="J24" s="3">
         <v>2200</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-574900</v>
+        <v>-589200</v>
       </c>
       <c r="E26" s="3">
-        <v>-464700</v>
+        <v>-476300</v>
       </c>
       <c r="F26" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="G26" s="3">
-        <v>-627900</v>
+        <v>-643500</v>
       </c>
       <c r="H26" s="3">
-        <v>-201000</v>
+        <v>-206000</v>
       </c>
       <c r="I26" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="J26" s="3">
-        <v>-1334700</v>
+        <v>-1367900</v>
       </c>
       <c r="K26" s="3">
         <v>-584800</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-574900</v>
+        <v>-589200</v>
       </c>
       <c r="E27" s="3">
-        <v>-464700</v>
+        <v>-476300</v>
       </c>
       <c r="F27" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="G27" s="3">
-        <v>-627900</v>
+        <v>-643500</v>
       </c>
       <c r="H27" s="3">
-        <v>-201000</v>
+        <v>-206000</v>
       </c>
       <c r="I27" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="J27" s="3">
-        <v>-1334700</v>
+        <v>-1367900</v>
       </c>
       <c r="K27" s="3">
         <v>-584800</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>22700</v>
+        <v>23300</v>
       </c>
       <c r="E32" s="3">
-        <v>-356600</v>
+        <v>-365500</v>
       </c>
       <c r="F32" s="3">
-        <v>-210700</v>
+        <v>-216000</v>
       </c>
       <c r="G32" s="3">
-        <v>405300</v>
+        <v>415400</v>
       </c>
       <c r="H32" s="3">
-        <v>21600</v>
+        <v>22200</v>
       </c>
       <c r="I32" s="3">
-        <v>139400</v>
+        <v>142900</v>
       </c>
       <c r="J32" s="3">
-        <v>920800</v>
+        <v>943700</v>
       </c>
       <c r="K32" s="3">
         <v>199600</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-574900</v>
+        <v>-589200</v>
       </c>
       <c r="E33" s="3">
-        <v>-464700</v>
+        <v>-476300</v>
       </c>
       <c r="F33" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="G33" s="3">
-        <v>-627900</v>
+        <v>-643500</v>
       </c>
       <c r="H33" s="3">
-        <v>-201000</v>
+        <v>-206000</v>
       </c>
       <c r="I33" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="J33" s="3">
-        <v>-1334700</v>
+        <v>-1367900</v>
       </c>
       <c r="K33" s="3">
         <v>-584800</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-574900</v>
+        <v>-589200</v>
       </c>
       <c r="E35" s="3">
-        <v>-464700</v>
+        <v>-476300</v>
       </c>
       <c r="F35" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="G35" s="3">
-        <v>-627900</v>
+        <v>-643500</v>
       </c>
       <c r="H35" s="3">
-        <v>-201000</v>
+        <v>-206000</v>
       </c>
       <c r="I35" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="J35" s="3">
-        <v>-1334700</v>
+        <v>-1367900</v>
       </c>
       <c r="K35" s="3">
         <v>-584800</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3365300</v>
+        <v>3449100</v>
       </c>
       <c r="E41" s="3">
-        <v>2683400</v>
+        <v>2750200</v>
       </c>
       <c r="F41" s="3">
-        <v>2965400</v>
+        <v>3039300</v>
       </c>
       <c r="G41" s="3">
-        <v>1243900</v>
+        <v>1274800</v>
       </c>
       <c r="H41" s="3">
-        <v>1150900</v>
+        <v>1179600</v>
       </c>
       <c r="I41" s="3">
-        <v>962900</v>
+        <v>986900</v>
       </c>
       <c r="J41" s="3">
-        <v>515500</v>
+        <v>528300</v>
       </c>
       <c r="K41" s="3">
         <v>819200</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1188800</v>
+        <v>1218400</v>
       </c>
       <c r="E42" s="3">
-        <v>937000</v>
+        <v>960300</v>
       </c>
       <c r="F42" s="3">
-        <v>817000</v>
+        <v>837300</v>
       </c>
       <c r="G42" s="3">
-        <v>644100</v>
+        <v>660100</v>
       </c>
       <c r="H42" s="3">
-        <v>747800</v>
+        <v>766500</v>
       </c>
       <c r="I42" s="3">
-        <v>988800</v>
+        <v>1013500</v>
       </c>
       <c r="J42" s="3">
-        <v>1115300</v>
+        <v>1143000</v>
       </c>
       <c r="K42" s="3">
         <v>900500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>948900</v>
+        <v>972500</v>
       </c>
       <c r="E43" s="3">
-        <v>751100</v>
+        <v>769800</v>
       </c>
       <c r="F43" s="3">
-        <v>676500</v>
+        <v>693400</v>
       </c>
       <c r="G43" s="3">
-        <v>505800</v>
+        <v>518400</v>
       </c>
       <c r="H43" s="3">
-        <v>438800</v>
+        <v>449700</v>
       </c>
       <c r="I43" s="3">
-        <v>434400</v>
+        <v>445300</v>
       </c>
       <c r="J43" s="3">
-        <v>389100</v>
+        <v>398700</v>
       </c>
       <c r="K43" s="3">
         <v>332000</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>181600</v>
+        <v>186100</v>
       </c>
       <c r="E45" s="3">
-        <v>331800</v>
+        <v>340000</v>
       </c>
       <c r="F45" s="3">
-        <v>265900</v>
+        <v>272500</v>
       </c>
       <c r="G45" s="3">
-        <v>163200</v>
+        <v>167200</v>
       </c>
       <c r="H45" s="3">
-        <v>73500</v>
+        <v>75300</v>
       </c>
       <c r="I45" s="3">
-        <v>41100</v>
+        <v>42100</v>
       </c>
       <c r="J45" s="3">
-        <v>31300</v>
+        <v>32100</v>
       </c>
       <c r="K45" s="3">
         <v>19500</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5684500</v>
+        <v>5826000</v>
       </c>
       <c r="E46" s="3">
-        <v>4703200</v>
+        <v>4820300</v>
       </c>
       <c r="F46" s="3">
-        <v>4724800</v>
+        <v>4842400</v>
       </c>
       <c r="G46" s="3">
-        <v>2556900</v>
+        <v>2620600</v>
       </c>
       <c r="H46" s="3">
-        <v>2411000</v>
+        <v>2471100</v>
       </c>
       <c r="I46" s="3">
-        <v>2427300</v>
+        <v>2487700</v>
       </c>
       <c r="J46" s="3">
-        <v>2051200</v>
+        <v>2102200</v>
       </c>
       <c r="K46" s="3">
         <v>2071300</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1313100</v>
+        <v>1345700</v>
       </c>
       <c r="E47" s="3">
-        <v>1229800</v>
+        <v>1260400</v>
       </c>
       <c r="F47" s="3">
-        <v>989900</v>
+        <v>1014600</v>
       </c>
       <c r="G47" s="3">
-        <v>2460800</v>
+        <v>2522000</v>
       </c>
       <c r="H47" s="3">
-        <v>1617800</v>
+        <v>1658100</v>
       </c>
       <c r="I47" s="3">
-        <v>1778800</v>
+        <v>1823100</v>
       </c>
       <c r="J47" s="3">
-        <v>984500</v>
+        <v>1009000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>591100</v>
+        <v>605900</v>
       </c>
       <c r="E48" s="3">
-        <v>826700</v>
+        <v>847300</v>
       </c>
       <c r="F48" s="3">
-        <v>874300</v>
+        <v>896000</v>
       </c>
       <c r="G48" s="3">
-        <v>818100</v>
+        <v>838500</v>
       </c>
       <c r="H48" s="3">
-        <v>842900</v>
+        <v>863900</v>
       </c>
       <c r="I48" s="3">
-        <v>212900</v>
+        <v>218200</v>
       </c>
       <c r="J48" s="3">
-        <v>78900</v>
+        <v>80900</v>
       </c>
       <c r="K48" s="3">
         <v>92200</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1319500</v>
+        <v>1352400</v>
       </c>
       <c r="E49" s="3">
-        <v>1399500</v>
+        <v>1434300</v>
       </c>
       <c r="F49" s="3">
-        <v>1062300</v>
+        <v>1088800</v>
       </c>
       <c r="G49" s="3">
-        <v>900200</v>
+        <v>922600</v>
       </c>
       <c r="H49" s="3">
-        <v>579300</v>
+        <v>593700</v>
       </c>
       <c r="I49" s="3">
-        <v>188000</v>
+        <v>192700</v>
       </c>
       <c r="J49" s="3">
-        <v>175100</v>
+        <v>179400</v>
       </c>
       <c r="K49" s="3">
         <v>86800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>111300</v>
+        <v>114100</v>
       </c>
       <c r="E52" s="3">
-        <v>92900</v>
+        <v>95300</v>
       </c>
       <c r="F52" s="3">
-        <v>97300</v>
+        <v>99700</v>
       </c>
       <c r="G52" s="3">
-        <v>100500</v>
+        <v>103000</v>
       </c>
       <c r="H52" s="3">
-        <v>84300</v>
+        <v>86400</v>
       </c>
       <c r="I52" s="3">
-        <v>78900</v>
+        <v>80900</v>
       </c>
       <c r="J52" s="3">
-        <v>68100</v>
+        <v>69800</v>
       </c>
       <c r="K52" s="3">
         <v>28200</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9019500</v>
+        <v>9244000</v>
       </c>
       <c r="E54" s="3">
-        <v>8252200</v>
+        <v>8457600</v>
       </c>
       <c r="F54" s="3">
-        <v>7748600</v>
+        <v>7941500</v>
       </c>
       <c r="G54" s="3">
-        <v>6836500</v>
+        <v>7006700</v>
       </c>
       <c r="H54" s="3">
-        <v>5535300</v>
+        <v>5673100</v>
       </c>
       <c r="I54" s="3">
-        <v>4685900</v>
+        <v>4802600</v>
       </c>
       <c r="J54" s="3">
-        <v>3357700</v>
+        <v>3441300</v>
       </c>
       <c r="K54" s="3">
         <v>2278500</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>715400</v>
+        <v>733200</v>
       </c>
       <c r="E57" s="3">
-        <v>635500</v>
+        <v>651300</v>
       </c>
       <c r="F57" s="3">
-        <v>577100</v>
+        <v>591500</v>
       </c>
       <c r="G57" s="3">
-        <v>469000</v>
+        <v>480700</v>
       </c>
       <c r="H57" s="3">
-        <v>407400</v>
+        <v>417600</v>
       </c>
       <c r="I57" s="3">
-        <v>318800</v>
+        <v>326700</v>
       </c>
       <c r="J57" s="3">
-        <v>261500</v>
+        <v>268000</v>
       </c>
       <c r="K57" s="3">
         <v>150800</v>
@@ -2719,7 +2719,7 @@
         <v>3</v>
       </c>
       <c r="H58" s="3">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3704600</v>
+        <v>3796900</v>
       </c>
       <c r="E59" s="3">
-        <v>3164300</v>
+        <v>3243100</v>
       </c>
       <c r="F59" s="3">
-        <v>2909200</v>
+        <v>2981700</v>
       </c>
       <c r="G59" s="3">
-        <v>2665000</v>
+        <v>2731300</v>
       </c>
       <c r="H59" s="3">
-        <v>2220800</v>
+        <v>2276100</v>
       </c>
       <c r="I59" s="3">
-        <v>2001500</v>
+        <v>2051300</v>
       </c>
       <c r="J59" s="3">
-        <v>1747500</v>
+        <v>1791000</v>
       </c>
       <c r="K59" s="3">
         <v>1167500</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4420100</v>
+        <v>4530100</v>
       </c>
       <c r="E60" s="3">
-        <v>3799700</v>
+        <v>3894300</v>
       </c>
       <c r="F60" s="3">
-        <v>3486300</v>
+        <v>3573100</v>
       </c>
       <c r="G60" s="3">
-        <v>3134000</v>
+        <v>3212000</v>
       </c>
       <c r="H60" s="3">
-        <v>2635800</v>
+        <v>2701400</v>
       </c>
       <c r="I60" s="3">
-        <v>2320300</v>
+        <v>2378000</v>
       </c>
       <c r="J60" s="3">
-        <v>2010100</v>
+        <v>2060100</v>
       </c>
       <c r="K60" s="3">
         <v>1323700</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1832900</v>
+        <v>1878500</v>
       </c>
       <c r="E61" s="3">
-        <v>1818800</v>
+        <v>1864100</v>
       </c>
       <c r="F61" s="3">
-        <v>1924700</v>
+        <v>1972600</v>
       </c>
       <c r="G61" s="3">
-        <v>623600</v>
+        <v>639100</v>
       </c>
       <c r="H61" s="3">
-        <v>672200</v>
+        <v>688900</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>1020200</v>
+        <v>1045600</v>
       </c>
       <c r="K61" s="3">
         <v>1201100</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>40000</v>
+        <v>41000</v>
       </c>
       <c r="E62" s="3">
-        <v>38900</v>
+        <v>39900</v>
       </c>
       <c r="F62" s="3">
-        <v>47600</v>
+        <v>48700</v>
       </c>
       <c r="G62" s="3">
-        <v>47600</v>
+        <v>48700</v>
       </c>
       <c r="H62" s="3">
-        <v>25900</v>
+        <v>26600</v>
       </c>
       <c r="I62" s="3">
-        <v>102700</v>
+        <v>105200</v>
       </c>
       <c r="J62" s="3">
-        <v>70200</v>
+        <v>72000</v>
       </c>
       <c r="K62" s="3">
         <v>14100</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6292900</v>
+        <v>6449600</v>
       </c>
       <c r="E66" s="3">
-        <v>5657500</v>
+        <v>5798300</v>
       </c>
       <c r="F66" s="3">
-        <v>5458600</v>
+        <v>5594500</v>
       </c>
       <c r="G66" s="3">
-        <v>3805100</v>
+        <v>3899900</v>
       </c>
       <c r="H66" s="3">
-        <v>3334000</v>
+        <v>3416900</v>
       </c>
       <c r="I66" s="3">
-        <v>2422900</v>
+        <v>2483200</v>
       </c>
       <c r="J66" s="3">
-        <v>3100500</v>
+        <v>3177700</v>
       </c>
       <c r="K66" s="3">
         <v>2538900</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-4519500</v>
+        <v>-4632000</v>
       </c>
       <c r="E72" s="3">
-        <v>-3941300</v>
+        <v>-4039400</v>
       </c>
       <c r="F72" s="3">
-        <v>-3479900</v>
+        <v>-3566500</v>
       </c>
       <c r="G72" s="3">
-        <v>-3555500</v>
+        <v>-3644000</v>
       </c>
       <c r="H72" s="3">
-        <v>-2927600</v>
+        <v>-3000500</v>
       </c>
       <c r="I72" s="3">
-        <v>-2707200</v>
+        <v>-2774500</v>
       </c>
       <c r="J72" s="3">
-        <v>-2622900</v>
+        <v>-2688100</v>
       </c>
       <c r="K72" s="3">
         <v>-1293300</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2726600</v>
+        <v>2794500</v>
       </c>
       <c r="E76" s="3">
-        <v>2594800</v>
+        <v>2659300</v>
       </c>
       <c r="F76" s="3">
-        <v>2290000</v>
+        <v>2347000</v>
       </c>
       <c r="G76" s="3">
-        <v>3031400</v>
+        <v>3106800</v>
       </c>
       <c r="H76" s="3">
-        <v>2201400</v>
+        <v>2256200</v>
       </c>
       <c r="I76" s="3">
-        <v>2263000</v>
+        <v>2319300</v>
       </c>
       <c r="J76" s="3">
-        <v>257200</v>
+        <v>263600</v>
       </c>
       <c r="K76" s="3">
         <v>-260400</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-574900</v>
+        <v>-589200</v>
       </c>
       <c r="E81" s="3">
-        <v>-464700</v>
+        <v>-476300</v>
       </c>
       <c r="F81" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="G81" s="3">
-        <v>-627900</v>
+        <v>-643500</v>
       </c>
       <c r="H81" s="3">
-        <v>-201000</v>
+        <v>-206000</v>
       </c>
       <c r="I81" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="J81" s="3">
-        <v>-1334700</v>
+        <v>-1367900</v>
       </c>
       <c r="K81" s="3">
         <v>-584800</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>170800</v>
+        <v>175000</v>
       </c>
       <c r="E83" s="3">
-        <v>184800</v>
+        <v>189400</v>
       </c>
       <c r="F83" s="3">
-        <v>137200</v>
+        <v>140700</v>
       </c>
       <c r="G83" s="3">
-        <v>120000</v>
+        <v>122900</v>
       </c>
       <c r="H83" s="3">
-        <v>94000</v>
+        <v>96400</v>
       </c>
       <c r="I83" s="3">
-        <v>34600</v>
+        <v>35400</v>
       </c>
       <c r="J83" s="3">
-        <v>58400</v>
+        <v>59800</v>
       </c>
       <c r="K83" s="3">
         <v>41200</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>734900</v>
+        <v>753200</v>
       </c>
       <c r="E89" s="3">
-        <v>49700</v>
+        <v>50900</v>
       </c>
       <c r="F89" s="3">
-        <v>390100</v>
+        <v>399800</v>
       </c>
       <c r="G89" s="3">
-        <v>279900</v>
+        <v>286900</v>
       </c>
       <c r="H89" s="3">
-        <v>619200</v>
+        <v>634700</v>
       </c>
       <c r="I89" s="3">
-        <v>371800</v>
+        <v>381000</v>
       </c>
       <c r="J89" s="3">
-        <v>193400</v>
+        <v>198300</v>
       </c>
       <c r="K89" s="3">
         <v>109600</v>
@@ -4029,25 +4029,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="E91" s="3">
-        <v>-27000</v>
+        <v>-27700</v>
       </c>
       <c r="F91" s="3">
-        <v>-91900</v>
+        <v>-94100</v>
       </c>
       <c r="G91" s="3">
-        <v>-84300</v>
+        <v>-86400</v>
       </c>
       <c r="H91" s="3">
-        <v>-145900</v>
+        <v>-149500</v>
       </c>
       <c r="I91" s="3">
-        <v>-135100</v>
+        <v>-138500</v>
       </c>
       <c r="J91" s="3">
-        <v>-38900</v>
+        <v>-39900</v>
       </c>
       <c r="K91" s="3">
         <v>-29300</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-234500</v>
+        <v>-240300</v>
       </c>
       <c r="E94" s="3">
-        <v>-457100</v>
+        <v>-468500</v>
       </c>
       <c r="F94" s="3">
-        <v>-202100</v>
+        <v>-207100</v>
       </c>
       <c r="G94" s="3">
-        <v>-402000</v>
+        <v>-412000</v>
       </c>
       <c r="H94" s="3">
-        <v>-235600</v>
+        <v>-241500</v>
       </c>
       <c r="I94" s="3">
-        <v>-23800</v>
+        <v>-24400</v>
       </c>
       <c r="J94" s="3">
-        <v>-470100</v>
+        <v>-481800</v>
       </c>
       <c r="K94" s="3">
         <v>-897300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>252900</v>
+        <v>259200</v>
       </c>
       <c r="E100" s="3">
-        <v>-43200</v>
+        <v>-44300</v>
       </c>
       <c r="F100" s="3">
-        <v>1350900</v>
+        <v>1384500</v>
       </c>
       <c r="G100" s="3">
-        <v>308000</v>
+        <v>315700</v>
       </c>
       <c r="H100" s="3">
-        <v>-219400</v>
+        <v>-224800</v>
       </c>
       <c r="I100" s="3">
-        <v>99400</v>
+        <v>101900</v>
       </c>
       <c r="J100" s="3">
-        <v>36700</v>
+        <v>37700</v>
       </c>
       <c r="K100" s="3">
         <v>993900</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-71300</v>
+        <v>-73100</v>
       </c>
       <c r="E101" s="3">
-        <v>168600</v>
+        <v>172800</v>
       </c>
       <c r="F101" s="3">
-        <v>182600</v>
+        <v>187200</v>
       </c>
       <c r="G101" s="3">
-        <v>-92900</v>
+        <v>-95300</v>
       </c>
       <c r="H101" s="3">
-        <v>23800</v>
+        <v>24400</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
-        <v>-60500</v>
+        <v>-62000</v>
       </c>
       <c r="K101" s="3">
         <v>-34700</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>681900</v>
+        <v>698900</v>
       </c>
       <c r="E102" s="3">
-        <v>-282100</v>
+        <v>-289100</v>
       </c>
       <c r="F102" s="3">
-        <v>1721600</v>
+        <v>1764400</v>
       </c>
       <c r="G102" s="3">
-        <v>92900</v>
+        <v>95300</v>
       </c>
       <c r="H102" s="3">
-        <v>188000</v>
+        <v>192700</v>
       </c>
       <c r="I102" s="3">
-        <v>447400</v>
+        <v>458500</v>
       </c>
       <c r="J102" s="3">
-        <v>-300400</v>
+        <v>-307900</v>
       </c>
       <c r="K102" s="3">
         <v>171400</v>

--- a/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>SPOT</t>
   </si>
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>14672400</v>
+        <v>14642400</v>
       </c>
       <c r="E8" s="3">
-        <v>12988800</v>
+        <v>12532900</v>
       </c>
       <c r="F8" s="3">
-        <v>10708300</v>
+        <v>10995100</v>
       </c>
       <c r="G8" s="3">
-        <v>8727900</v>
+        <v>9639100</v>
       </c>
       <c r="H8" s="3">
-        <v>7491800</v>
+        <v>7590600</v>
       </c>
       <c r="I8" s="3">
-        <v>5824900</v>
+        <v>6021300</v>
       </c>
       <c r="J8" s="3">
-        <v>4530100</v>
+        <v>4911100</v>
       </c>
       <c r="K8" s="3">
         <v>3202900</v>
@@ -772,25 +772,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>10885500</v>
+        <v>10831200</v>
       </c>
       <c r="E9" s="3">
-        <v>9748000</v>
+        <v>9405800</v>
       </c>
       <c r="F9" s="3">
-        <v>7838500</v>
+        <v>8048400</v>
       </c>
       <c r="G9" s="3">
-        <v>6496100</v>
+        <v>7174300</v>
       </c>
       <c r="H9" s="3">
-        <v>5584500</v>
+        <v>5658200</v>
       </c>
       <c r="I9" s="3">
-        <v>4326300</v>
+        <v>4472200</v>
       </c>
       <c r="J9" s="3">
-        <v>3589700</v>
+        <v>3891700</v>
       </c>
       <c r="K9" s="3">
         <v>2767800</v>
@@ -817,25 +817,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3786900</v>
+        <v>3811200</v>
       </c>
       <c r="E10" s="3">
-        <v>3240800</v>
+        <v>3127100</v>
       </c>
       <c r="F10" s="3">
-        <v>2869800</v>
+        <v>2946700</v>
       </c>
       <c r="G10" s="3">
-        <v>2231800</v>
+        <v>2464800</v>
       </c>
       <c r="H10" s="3">
-        <v>1907300</v>
+        <v>1932400</v>
       </c>
       <c r="I10" s="3">
-        <v>1498600</v>
+        <v>1549100</v>
       </c>
       <c r="J10" s="3">
-        <v>940400</v>
+        <v>1019500</v>
       </c>
       <c r="K10" s="3">
         <v>435100</v>
@@ -881,25 +881,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1695700</v>
+        <v>1692300</v>
       </c>
       <c r="E12" s="3">
-        <v>1491900</v>
+        <v>1482300</v>
       </c>
       <c r="F12" s="3">
-        <v>982400</v>
+        <v>1037200</v>
       </c>
       <c r="G12" s="3">
-        <v>907100</v>
+        <v>1023900</v>
       </c>
       <c r="H12" s="3">
-        <v>665700</v>
+        <v>690200</v>
       </c>
       <c r="I12" s="3">
-        <v>546000</v>
+        <v>564500</v>
       </c>
       <c r="J12" s="3">
-        <v>438600</v>
+        <v>475500</v>
       </c>
       <c r="K12" s="3">
         <v>224600</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>371000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+        <v>402300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>15700</v>
       </c>
       <c r="I14" s="3">
-        <v>1100</v>
+        <v>2300</v>
       </c>
       <c r="J14" s="3">
-        <v>-1100</v>
+        <v>1200</v>
       </c>
       <c r="K14" s="3">
         <v>2200</v>
@@ -1015,26 +1015,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>101700</v>
       </c>
       <c r="E15" s="3">
-        <v>44300</v>
+        <v>101500</v>
       </c>
       <c r="F15" s="3">
-        <v>27700</v>
+        <v>144400</v>
       </c>
       <c r="G15" s="3">
-        <v>19900</v>
+        <v>135800</v>
       </c>
       <c r="H15" s="3">
-        <v>15500</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>97600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>36600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>64800</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15166400</v>
+        <v>14733100</v>
       </c>
       <c r="E17" s="3">
-        <v>13718700</v>
+        <v>13237100</v>
       </c>
       <c r="F17" s="3">
-        <v>10604200</v>
+        <v>10888200</v>
       </c>
       <c r="G17" s="3">
-        <v>9052400</v>
+        <v>9997600</v>
       </c>
       <c r="H17" s="3">
-        <v>7572700</v>
+        <v>7656800</v>
       </c>
       <c r="I17" s="3">
-        <v>5873600</v>
+        <v>6070500</v>
       </c>
       <c r="J17" s="3">
-        <v>4947600</v>
+        <v>5365000</v>
       </c>
       <c r="K17" s="3">
         <v>3583800</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-494000</v>
+        <v>-90600</v>
       </c>
       <c r="E18" s="3">
-        <v>-729900</v>
+        <v>-704300</v>
       </c>
       <c r="F18" s="3">
-        <v>104100</v>
+        <v>106900</v>
       </c>
       <c r="G18" s="3">
-        <v>-324500</v>
+        <v>-358400</v>
       </c>
       <c r="H18" s="3">
-        <v>-80900</v>
+        <v>-66200</v>
       </c>
       <c r="I18" s="3">
-        <v>-48700</v>
+        <v>-49200</v>
       </c>
       <c r="J18" s="3">
-        <v>-417600</v>
+        <v>-453900</v>
       </c>
       <c r="K18" s="3">
         <v>-380800</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-23300</v>
+        <v>155900</v>
       </c>
       <c r="E20" s="3">
-        <v>365500</v>
+        <v>-320600</v>
       </c>
       <c r="F20" s="3">
-        <v>216000</v>
+        <v>-242200</v>
       </c>
       <c r="G20" s="3">
-        <v>-415400</v>
+        <v>463600</v>
       </c>
       <c r="H20" s="3">
-        <v>-22200</v>
+        <v>51600</v>
       </c>
       <c r="I20" s="3">
-        <v>-142900</v>
+        <v>168300</v>
       </c>
       <c r="J20" s="3">
-        <v>-943700</v>
+        <v>1044700</v>
       </c>
       <c r="K20" s="3">
         <v>-199600</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-342300</v>
+        <v>-144800</v>
       </c>
       <c r="E21" s="3">
-        <v>-175000</v>
+        <v>-282100</v>
       </c>
       <c r="F21" s="3">
-        <v>460700</v>
+        <v>493600</v>
       </c>
       <c r="G21" s="3">
-        <v>-617000</v>
+        <v>-686200</v>
       </c>
       <c r="H21" s="3">
-        <v>-6700</v>
+        <v>-20200</v>
       </c>
       <c r="I21" s="3">
-        <v>-156200</v>
+        <v>-180900</v>
       </c>
       <c r="J21" s="3">
-        <v>-1301400</v>
+        <v>-1433700</v>
       </c>
       <c r="K21" s="3">
         <v>-539300</v>
@@ -1276,25 +1276,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>42100</v>
+        <v>54200</v>
       </c>
       <c r="E22" s="3">
-        <v>45400</v>
+        <v>62000</v>
       </c>
       <c r="F22" s="3">
-        <v>44300</v>
+        <v>58000</v>
       </c>
       <c r="G22" s="3">
-        <v>45400</v>
+        <v>66100</v>
       </c>
       <c r="H22" s="3">
-        <v>42100</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+        <v>48300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>6900</v>
       </c>
       <c r="J22" s="3">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1321,25 +1321,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-559300</v>
+        <v>-558200</v>
       </c>
       <c r="E23" s="3">
-        <v>-409800</v>
+        <v>-395400</v>
       </c>
       <c r="F23" s="3">
-        <v>275800</v>
+        <v>283200</v>
       </c>
       <c r="G23" s="3">
-        <v>-785300</v>
+        <v>-867300</v>
       </c>
       <c r="H23" s="3">
-        <v>-145100</v>
+        <v>-147000</v>
       </c>
       <c r="I23" s="3">
-        <v>-191600</v>
+        <v>-198100</v>
       </c>
       <c r="J23" s="3">
-        <v>-1365700</v>
+        <v>-1480500</v>
       </c>
       <c r="K23" s="3">
         <v>-580500</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>29900</v>
+        <v>29800</v>
       </c>
       <c r="E24" s="3">
-        <v>66500</v>
+        <v>64100</v>
       </c>
       <c r="F24" s="3">
-        <v>313500</v>
+        <v>321800</v>
       </c>
       <c r="G24" s="3">
-        <v>-141800</v>
+        <v>-156600</v>
       </c>
       <c r="H24" s="3">
-        <v>60900</v>
+        <v>61700</v>
       </c>
       <c r="I24" s="3">
-        <v>-105200</v>
+        <v>-108800</v>
       </c>
       <c r="J24" s="3">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="K24" s="3">
         <v>4300</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-589200</v>
+        <v>-588000</v>
       </c>
       <c r="E26" s="3">
-        <v>-476300</v>
+        <v>-459500</v>
       </c>
       <c r="F26" s="3">
-        <v>-37700</v>
+        <v>-38700</v>
       </c>
       <c r="G26" s="3">
-        <v>-643500</v>
+        <v>-710700</v>
       </c>
       <c r="H26" s="3">
-        <v>-206000</v>
+        <v>-208700</v>
       </c>
       <c r="I26" s="3">
-        <v>-86400</v>
+        <v>-89300</v>
       </c>
       <c r="J26" s="3">
-        <v>-1367900</v>
+        <v>-1482900</v>
       </c>
       <c r="K26" s="3">
         <v>-584800</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-589200</v>
+        <v>-588000</v>
       </c>
       <c r="E27" s="3">
-        <v>-476300</v>
+        <v>-459600</v>
       </c>
       <c r="F27" s="3">
-        <v>-37700</v>
+        <v>-38700</v>
       </c>
       <c r="G27" s="3">
-        <v>-643500</v>
+        <v>-710700</v>
       </c>
       <c r="H27" s="3">
-        <v>-206000</v>
+        <v>-208700</v>
       </c>
       <c r="I27" s="3">
-        <v>-86400</v>
+        <v>-89300</v>
       </c>
       <c r="J27" s="3">
-        <v>-1367900</v>
+        <v>-1483000</v>
       </c>
       <c r="K27" s="3">
         <v>-584800</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>23300</v>
+        <v>-155900</v>
       </c>
       <c r="E32" s="3">
-        <v>-365500</v>
+        <v>320600</v>
       </c>
       <c r="F32" s="3">
-        <v>-216000</v>
+        <v>242200</v>
       </c>
       <c r="G32" s="3">
-        <v>415400</v>
+        <v>-463600</v>
       </c>
       <c r="H32" s="3">
-        <v>22200</v>
+        <v>-51600</v>
       </c>
       <c r="I32" s="3">
-        <v>142900</v>
+        <v>-168300</v>
       </c>
       <c r="J32" s="3">
-        <v>943700</v>
+        <v>-1044700</v>
       </c>
       <c r="K32" s="3">
         <v>199600</v>
@@ -1771,25 +1771,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-589200</v>
+        <v>-588000</v>
       </c>
       <c r="E33" s="3">
-        <v>-476300</v>
+        <v>-459500</v>
       </c>
       <c r="F33" s="3">
-        <v>-37700</v>
+        <v>-38700</v>
       </c>
       <c r="G33" s="3">
-        <v>-643500</v>
+        <v>-710700</v>
       </c>
       <c r="H33" s="3">
-        <v>-206000</v>
+        <v>-208700</v>
       </c>
       <c r="I33" s="3">
-        <v>-86400</v>
+        <v>-89300</v>
       </c>
       <c r="J33" s="3">
-        <v>-1367900</v>
+        <v>-1482900</v>
       </c>
       <c r="K33" s="3">
         <v>-584800</v>
@@ -1861,25 +1861,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-589200</v>
+        <v>-588000</v>
       </c>
       <c r="E35" s="3">
-        <v>-476300</v>
+        <v>-459500</v>
       </c>
       <c r="F35" s="3">
-        <v>-37700</v>
+        <v>-38700</v>
       </c>
       <c r="G35" s="3">
-        <v>-643500</v>
+        <v>-710700</v>
       </c>
       <c r="H35" s="3">
-        <v>-206000</v>
+        <v>-208700</v>
       </c>
       <c r="I35" s="3">
-        <v>-86400</v>
+        <v>-89300</v>
       </c>
       <c r="J35" s="3">
-        <v>-1367900</v>
+        <v>-1482900</v>
       </c>
       <c r="K35" s="3">
         <v>-584800</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3449100</v>
+        <v>3442000</v>
       </c>
       <c r="E41" s="3">
-        <v>2750200</v>
+        <v>2653600</v>
       </c>
       <c r="F41" s="3">
-        <v>3039300</v>
+        <v>3120700</v>
       </c>
       <c r="G41" s="3">
-        <v>1274800</v>
+        <v>1408000</v>
       </c>
       <c r="H41" s="3">
-        <v>1179600</v>
+        <v>1195200</v>
       </c>
       <c r="I41" s="3">
-        <v>986900</v>
+        <v>1020200</v>
       </c>
       <c r="J41" s="3">
-        <v>528300</v>
+        <v>572800</v>
       </c>
       <c r="K41" s="3">
         <v>819200</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1218400</v>
+        <v>949500</v>
       </c>
       <c r="E42" s="3">
-        <v>960300</v>
+        <v>926600</v>
       </c>
       <c r="F42" s="3">
-        <v>837300</v>
+        <v>783600</v>
       </c>
       <c r="G42" s="3">
-        <v>660100</v>
+        <v>391400</v>
       </c>
       <c r="H42" s="3">
-        <v>766500</v>
+        <v>601500</v>
       </c>
       <c r="I42" s="3">
-        <v>1013500</v>
+        <v>653800</v>
       </c>
       <c r="J42" s="3">
-        <v>1143000</v>
+        <v>697600</v>
       </c>
       <c r="K42" s="3">
         <v>900500</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>972500</v>
+        <v>970500</v>
       </c>
       <c r="E43" s="3">
-        <v>769800</v>
+        <v>742800</v>
       </c>
       <c r="F43" s="3">
-        <v>693400</v>
+        <v>711900</v>
       </c>
       <c r="G43" s="3">
-        <v>518400</v>
+        <v>572500</v>
       </c>
       <c r="H43" s="3">
-        <v>449700</v>
+        <v>455600</v>
       </c>
       <c r="I43" s="3">
-        <v>445300</v>
+        <v>460300</v>
       </c>
       <c r="J43" s="3">
-        <v>398700</v>
+        <v>432300</v>
       </c>
       <c r="K43" s="3">
         <v>332000</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>186100</v>
+        <v>381300</v>
       </c>
       <c r="E45" s="3">
-        <v>340000</v>
+        <v>233000</v>
       </c>
       <c r="F45" s="3">
-        <v>272500</v>
+        <v>271800</v>
       </c>
       <c r="G45" s="3">
-        <v>167200</v>
+        <v>464800</v>
       </c>
       <c r="H45" s="3">
-        <v>75300</v>
+        <v>211000</v>
       </c>
       <c r="I45" s="3">
-        <v>42100</v>
+        <v>437400</v>
       </c>
       <c r="J45" s="3">
-        <v>32100</v>
+        <v>576400</v>
       </c>
       <c r="K45" s="3">
         <v>19500</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5826000</v>
+        <v>5814100</v>
       </c>
       <c r="E46" s="3">
-        <v>4820300</v>
+        <v>4651100</v>
       </c>
       <c r="F46" s="3">
-        <v>4842400</v>
+        <v>4972100</v>
       </c>
       <c r="G46" s="3">
-        <v>2620600</v>
+        <v>2894200</v>
       </c>
       <c r="H46" s="3">
-        <v>2471100</v>
+        <v>2503600</v>
       </c>
       <c r="I46" s="3">
-        <v>2487700</v>
+        <v>2571600</v>
       </c>
       <c r="J46" s="3">
-        <v>2102200</v>
+        <v>2279100</v>
       </c>
       <c r="K46" s="3">
         <v>2071300</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1345700</v>
+        <v>1343000</v>
       </c>
       <c r="E47" s="3">
-        <v>1260400</v>
+        <v>1216200</v>
       </c>
       <c r="F47" s="3">
-        <v>1014600</v>
+        <v>1041700</v>
       </c>
       <c r="G47" s="3">
-        <v>2522000</v>
+        <v>2785300</v>
       </c>
       <c r="H47" s="3">
-        <v>1658100</v>
+        <v>1679900</v>
       </c>
       <c r="I47" s="3">
-        <v>1823100</v>
+        <v>1884600</v>
       </c>
       <c r="J47" s="3">
-        <v>1009000</v>
+        <v>1093900</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>605900</v>
+        <v>604600</v>
       </c>
       <c r="E48" s="3">
-        <v>847300</v>
+        <v>817600</v>
       </c>
       <c r="F48" s="3">
-        <v>896000</v>
+        <v>920100</v>
       </c>
       <c r="G48" s="3">
-        <v>838500</v>
+        <v>926000</v>
       </c>
       <c r="H48" s="3">
-        <v>863900</v>
+        <v>875300</v>
       </c>
       <c r="I48" s="3">
-        <v>218200</v>
+        <v>225600</v>
       </c>
       <c r="J48" s="3">
-        <v>80900</v>
+        <v>87700</v>
       </c>
       <c r="K48" s="3">
         <v>92200</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1352400</v>
+        <v>1335200</v>
       </c>
       <c r="E49" s="3">
-        <v>1434300</v>
+        <v>1363700</v>
       </c>
       <c r="F49" s="3">
-        <v>1088800</v>
+        <v>1082700</v>
       </c>
       <c r="G49" s="3">
-        <v>922600</v>
+        <v>978600</v>
       </c>
       <c r="H49" s="3">
-        <v>593700</v>
+        <v>572300</v>
       </c>
       <c r="I49" s="3">
-        <v>192700</v>
+        <v>183200</v>
       </c>
       <c r="J49" s="3">
-        <v>179400</v>
+        <v>180100</v>
       </c>
       <c r="K49" s="3">
         <v>86800</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>114100</v>
+        <v>82900</v>
       </c>
       <c r="E52" s="3">
-        <v>95300</v>
+        <v>83400</v>
       </c>
       <c r="F52" s="3">
-        <v>99700</v>
+        <v>87600</v>
       </c>
       <c r="G52" s="3">
-        <v>103000</v>
+        <v>95400</v>
       </c>
       <c r="H52" s="3">
-        <v>86400</v>
+        <v>77400</v>
       </c>
       <c r="I52" s="3">
-        <v>80900</v>
+        <v>74400</v>
       </c>
       <c r="J52" s="3">
-        <v>69800</v>
+        <v>64800</v>
       </c>
       <c r="K52" s="3">
         <v>28200</v>
@@ -2579,25 +2579,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9244000</v>
+        <v>9225200</v>
       </c>
       <c r="E54" s="3">
-        <v>8457600</v>
+        <v>8160700</v>
       </c>
       <c r="F54" s="3">
-        <v>7941500</v>
+        <v>8154200</v>
       </c>
       <c r="G54" s="3">
-        <v>7006700</v>
+        <v>7738200</v>
       </c>
       <c r="H54" s="3">
-        <v>5673100</v>
+        <v>5748000</v>
       </c>
       <c r="I54" s="3">
-        <v>4802600</v>
+        <v>4964500</v>
       </c>
       <c r="J54" s="3">
-        <v>3441300</v>
+        <v>3730800</v>
       </c>
       <c r="K54" s="3">
         <v>2278500</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>733200</v>
+        <v>731700</v>
       </c>
       <c r="E57" s="3">
-        <v>651300</v>
+        <v>628400</v>
       </c>
       <c r="F57" s="3">
-        <v>591500</v>
+        <v>607300</v>
       </c>
       <c r="G57" s="3">
-        <v>480700</v>
+        <v>530900</v>
       </c>
       <c r="H57" s="3">
-        <v>417600</v>
+        <v>423100</v>
       </c>
       <c r="I57" s="3">
-        <v>326700</v>
+        <v>337800</v>
       </c>
       <c r="J57" s="3">
-        <v>268000</v>
+        <v>290600</v>
       </c>
       <c r="K57" s="3">
         <v>150800</v>
@@ -2706,26 +2706,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>62000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>50000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>37900</v>
       </c>
       <c r="H58" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>5400</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3796900</v>
+        <v>761600</v>
       </c>
       <c r="E59" s="3">
-        <v>3243100</v>
+        <v>623100</v>
       </c>
       <c r="F59" s="3">
-        <v>2981700</v>
+        <v>698300</v>
       </c>
       <c r="G59" s="3">
-        <v>2731300</v>
+        <v>643400</v>
       </c>
       <c r="H59" s="3">
-        <v>2276100</v>
+        <v>529700</v>
       </c>
       <c r="I59" s="3">
-        <v>2051300</v>
+        <v>755700</v>
       </c>
       <c r="J59" s="3">
-        <v>1791000</v>
+        <v>775700</v>
       </c>
       <c r="K59" s="3">
         <v>1167500</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4530100</v>
+        <v>4520800</v>
       </c>
       <c r="E60" s="3">
-        <v>3894300</v>
+        <v>3757600</v>
       </c>
       <c r="F60" s="3">
-        <v>3573100</v>
+        <v>3668800</v>
       </c>
       <c r="G60" s="3">
-        <v>3212000</v>
+        <v>3547400</v>
       </c>
       <c r="H60" s="3">
-        <v>2701400</v>
+        <v>2737100</v>
       </c>
       <c r="I60" s="3">
-        <v>2378000</v>
+        <v>2460500</v>
       </c>
       <c r="J60" s="3">
-        <v>2060100</v>
+        <v>2233400</v>
       </c>
       <c r="K60" s="3">
         <v>1323700</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1878500</v>
+        <v>1874700</v>
       </c>
       <c r="E61" s="3">
-        <v>1864100</v>
+        <v>1798700</v>
       </c>
       <c r="F61" s="3">
-        <v>1972600</v>
+        <v>2025500</v>
       </c>
       <c r="G61" s="3">
-        <v>639100</v>
+        <v>705800</v>
       </c>
       <c r="H61" s="3">
-        <v>688900</v>
+        <v>698000</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>1045600</v>
+        <v>1133500</v>
       </c>
       <c r="K61" s="3">
         <v>1201100</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>41000</v>
+        <v>32100</v>
       </c>
       <c r="E62" s="3">
-        <v>39900</v>
+        <v>33100</v>
       </c>
       <c r="F62" s="3">
-        <v>48700</v>
+        <v>50000</v>
       </c>
       <c r="G62" s="3">
-        <v>48700</v>
+        <v>53800</v>
       </c>
       <c r="H62" s="3">
-        <v>26600</v>
+        <v>24700</v>
       </c>
       <c r="I62" s="3">
-        <v>105200</v>
+        <v>104200</v>
       </c>
       <c r="J62" s="3">
-        <v>72000</v>
+        <v>74400</v>
       </c>
       <c r="K62" s="3">
         <v>14100</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6449600</v>
+        <v>6436400</v>
       </c>
       <c r="E66" s="3">
-        <v>5798300</v>
+        <v>5594700</v>
       </c>
       <c r="F66" s="3">
-        <v>5594500</v>
+        <v>5744300</v>
       </c>
       <c r="G66" s="3">
-        <v>3899900</v>
+        <v>4307000</v>
       </c>
       <c r="H66" s="3">
-        <v>3416900</v>
+        <v>3462000</v>
       </c>
       <c r="I66" s="3">
-        <v>2483200</v>
+        <v>2567000</v>
       </c>
       <c r="J66" s="3">
-        <v>3177700</v>
+        <v>3445000</v>
       </c>
       <c r="K66" s="3">
         <v>2538900</v>
@@ -3311,25 +3311,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-4632000</v>
+        <v>-4622500</v>
       </c>
       <c r="E72" s="3">
-        <v>-4039400</v>
+        <v>-3897600</v>
       </c>
       <c r="F72" s="3">
-        <v>-3566500</v>
+        <v>-3662000</v>
       </c>
       <c r="G72" s="3">
-        <v>-3644000</v>
+        <v>-4024500</v>
       </c>
       <c r="H72" s="3">
-        <v>-3000500</v>
+        <v>-3040100</v>
       </c>
       <c r="I72" s="3">
-        <v>-2774500</v>
+        <v>-2868100</v>
       </c>
       <c r="J72" s="3">
-        <v>-2688100</v>
+        <v>-2914300</v>
       </c>
       <c r="K72" s="3">
         <v>-1293300</v>
@@ -3491,25 +3491,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2794500</v>
+        <v>2788800</v>
       </c>
       <c r="E76" s="3">
-        <v>2659300</v>
+        <v>2566000</v>
       </c>
       <c r="F76" s="3">
-        <v>2347000</v>
+        <v>2409900</v>
       </c>
       <c r="G76" s="3">
-        <v>3106800</v>
+        <v>3431200</v>
       </c>
       <c r="H76" s="3">
-        <v>2256200</v>
+        <v>2285900</v>
       </c>
       <c r="I76" s="3">
-        <v>2319300</v>
+        <v>2397500</v>
       </c>
       <c r="J76" s="3">
-        <v>263600</v>
+        <v>285800</v>
       </c>
       <c r="K76" s="3">
         <v>-260400</v>
@@ -3631,25 +3631,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-589200</v>
+        <v>-588000</v>
       </c>
       <c r="E81" s="3">
-        <v>-476300</v>
+        <v>-459500</v>
       </c>
       <c r="F81" s="3">
-        <v>-37700</v>
+        <v>-38700</v>
       </c>
       <c r="G81" s="3">
-        <v>-643500</v>
+        <v>-710700</v>
       </c>
       <c r="H81" s="3">
-        <v>-206000</v>
+        <v>-208700</v>
       </c>
       <c r="I81" s="3">
-        <v>-86400</v>
+        <v>-89300</v>
       </c>
       <c r="J81" s="3">
-        <v>-1367900</v>
+        <v>-1482900</v>
       </c>
       <c r="K81" s="3">
         <v>-584800</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>175000</v>
+        <v>121600</v>
       </c>
       <c r="E83" s="3">
-        <v>189400</v>
+        <v>126100</v>
       </c>
       <c r="F83" s="3">
-        <v>140700</v>
+        <v>106900</v>
       </c>
       <c r="G83" s="3">
-        <v>122900</v>
+        <v>105200</v>
       </c>
       <c r="H83" s="3">
-        <v>96400</v>
+        <v>79700</v>
       </c>
       <c r="I83" s="3">
-        <v>35400</v>
+        <v>24000</v>
       </c>
       <c r="J83" s="3">
-        <v>59800</v>
+        <v>55200</v>
       </c>
       <c r="K83" s="3">
         <v>41200</v>
@@ -3965,25 +3965,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>753200</v>
+        <v>751600</v>
       </c>
       <c r="E89" s="3">
-        <v>50900</v>
+        <v>49200</v>
       </c>
       <c r="F89" s="3">
-        <v>399800</v>
+        <v>410600</v>
       </c>
       <c r="G89" s="3">
-        <v>286900</v>
+        <v>316800</v>
       </c>
       <c r="H89" s="3">
-        <v>634700</v>
+        <v>643000</v>
       </c>
       <c r="I89" s="3">
-        <v>381000</v>
+        <v>393900</v>
       </c>
       <c r="J89" s="3">
-        <v>198300</v>
+        <v>214900</v>
       </c>
       <c r="K89" s="3">
         <v>109600</v>
@@ -4032,22 +4032,22 @@
         <v>-6600</v>
       </c>
       <c r="E91" s="3">
-        <v>-27700</v>
+        <v>-26700</v>
       </c>
       <c r="F91" s="3">
-        <v>-94100</v>
+        <v>-96700</v>
       </c>
       <c r="G91" s="3">
-        <v>-86400</v>
+        <v>-95400</v>
       </c>
       <c r="H91" s="3">
-        <v>-149500</v>
+        <v>-151500</v>
       </c>
       <c r="I91" s="3">
-        <v>-138500</v>
+        <v>-143100</v>
       </c>
       <c r="J91" s="3">
-        <v>-39900</v>
+        <v>-43200</v>
       </c>
       <c r="K91" s="3">
         <v>-29300</v>
@@ -4164,25 +4164,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-240300</v>
+        <v>-239900</v>
       </c>
       <c r="E94" s="3">
-        <v>-468500</v>
+        <v>-452100</v>
       </c>
       <c r="F94" s="3">
-        <v>-207100</v>
+        <v>-212700</v>
       </c>
       <c r="G94" s="3">
-        <v>-412000</v>
+        <v>-455000</v>
       </c>
       <c r="H94" s="3">
-        <v>-241500</v>
+        <v>-244600</v>
       </c>
       <c r="I94" s="3">
-        <v>-24400</v>
+        <v>-25200</v>
       </c>
       <c r="J94" s="3">
-        <v>-481800</v>
+        <v>-522300</v>
       </c>
       <c r="K94" s="3">
         <v>-897300</v>
@@ -4408,25 +4408,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>259200</v>
+        <v>258600</v>
       </c>
       <c r="E100" s="3">
-        <v>-44300</v>
+        <v>-42700</v>
       </c>
       <c r="F100" s="3">
-        <v>1384500</v>
+        <v>1421600</v>
       </c>
       <c r="G100" s="3">
-        <v>315700</v>
+        <v>348600</v>
       </c>
       <c r="H100" s="3">
-        <v>-224800</v>
+        <v>-227800</v>
       </c>
       <c r="I100" s="3">
-        <v>101900</v>
+        <v>105300</v>
       </c>
       <c r="J100" s="3">
-        <v>37700</v>
+        <v>40800</v>
       </c>
       <c r="K100" s="3">
         <v>993900</v>
@@ -4453,25 +4453,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-73100</v>
+        <v>-73000</v>
       </c>
       <c r="E101" s="3">
-        <v>172800</v>
+        <v>166700</v>
       </c>
       <c r="F101" s="3">
-        <v>187200</v>
+        <v>192200</v>
       </c>
       <c r="G101" s="3">
-        <v>-95300</v>
+        <v>-105200</v>
       </c>
       <c r="H101" s="3">
-        <v>24400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+        <v>24700</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3">
-        <v>-62000</v>
+        <v>-67200</v>
       </c>
       <c r="K101" s="3">
         <v>-34700</v>
@@ -4498,25 +4498,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>698900</v>
+        <v>697500</v>
       </c>
       <c r="E102" s="3">
-        <v>-289100</v>
+        <v>-278900</v>
       </c>
       <c r="F102" s="3">
-        <v>1764400</v>
+        <v>1811700</v>
       </c>
       <c r="G102" s="3">
-        <v>95300</v>
+        <v>105200</v>
       </c>
       <c r="H102" s="3">
-        <v>192700</v>
+        <v>195300</v>
       </c>
       <c r="I102" s="3">
-        <v>458500</v>
+        <v>474000</v>
       </c>
       <c r="J102" s="3">
-        <v>-307900</v>
+        <v>-333800</v>
       </c>
       <c r="K102" s="3">
         <v>171400</v>

--- a/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
   <si>
     <t>SPOT</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>16226300</v>
+      </c>
+      <c r="E8" s="3">
         <v>14642400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12532900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10995100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9639100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7590600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6021300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4911100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3202900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1980400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1225100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>892400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11317900</v>
+      </c>
+      <c r="E9" s="3">
         <v>10831200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9405800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8048400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7174300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5658200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4472200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3891700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2767800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1749700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1028600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>739300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4908400</v>
+      </c>
+      <c r="E10" s="3">
         <v>3811200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3127100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2946700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2464800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1932400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1549100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1019500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>435100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>230700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>196500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>153100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1529100</v>
+      </c>
+      <c r="E12" s="3">
         <v>1692300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1482300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1037200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1023900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>690200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>564500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>475500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>224600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>138800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>128700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>87300</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,44 +980,47 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E14" s="3">
         <v>402300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>15700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1009,36 +1028,39 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>101700</v>
+        <v>71400</v>
       </c>
       <c r="E15" s="3">
-        <v>101500</v>
+        <v>99500</v>
       </c>
       <c r="F15" s="3">
+        <v>182800</v>
+      </c>
+      <c r="G15" s="3">
         <v>144400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>135800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>97600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>64800</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1048,15 +1070,18 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14768600</v>
+      </c>
+      <c r="E17" s="3">
         <v>14733100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13237100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10888200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9997600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7656800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6070500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5365000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3583800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2220200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1440700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1009600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1457700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-90600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-704300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>106900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-358400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-66200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-49200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-453900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-380800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-239900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-215700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-117200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,86 +1212,90 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>155900</v>
+        <v>238100</v>
       </c>
       <c r="E20" s="3">
-        <v>-320600</v>
+        <v>168000</v>
       </c>
       <c r="F20" s="3">
+        <v>-302400</v>
+      </c>
+      <c r="G20" s="3">
         <v>-242200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>463600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>51600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>168300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1044700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-199600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>10200</v>
       </c>
       <c r="M20" s="3">
         <v>10200</v>
       </c>
       <c r="N20" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O20" s="3">
         <v>44300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-144800</v>
+        <v>1291000</v>
       </c>
       <c r="E21" s="3">
-        <v>-282100</v>
+        <v>-159200</v>
       </c>
       <c r="F21" s="3">
+        <v>-219100</v>
+      </c>
+      <c r="G21" s="3">
         <v>493600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-686200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-180900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1433700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-539300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-199600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1269,36 +1305,39 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>54200</v>
+        <v>37300</v>
       </c>
       <c r="E22" s="3">
-        <v>62000</v>
+        <v>42000</v>
       </c>
       <c r="F22" s="3">
+        <v>43800</v>
+      </c>
+      <c r="G22" s="3">
         <v>58000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>66100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>48300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3600</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,99 +1353,108 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1388300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-558200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-395400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>283200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-867300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-147000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-198100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1480500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-580500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-229700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-205500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-73000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E24" s="3">
         <v>29800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>64100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>321800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-156600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-108800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1178200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-588000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-459500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-710700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-208700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-89300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1482900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-584800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-234800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-212300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-75400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1178200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-588000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-459600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-710700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-208700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-89300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1483000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-584800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-234800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-212300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-75400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-155900</v>
+        <v>-238100</v>
       </c>
       <c r="E32" s="3">
-        <v>320600</v>
+        <v>-168000</v>
       </c>
       <c r="F32" s="3">
+        <v>302400</v>
+      </c>
+      <c r="G32" s="3">
         <v>242200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-463600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-51600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-168300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1044700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>199600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-10200</v>
       </c>
       <c r="M32" s="3">
         <v>-10200</v>
       </c>
       <c r="N32" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="O32" s="3">
         <v>-44300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1178200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-588000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-459500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-710700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-208700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-89300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1482900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-584800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-234800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-212300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-75400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1178200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-588000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-459500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-710700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-208700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-89300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1482900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-584800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-234800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-212300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-75400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,131 +2073,138 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4949800</v>
+      </c>
+      <c r="E41" s="3">
         <v>3442000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2653600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3120700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1408000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1195200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1020200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>572800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>819200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>609400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>232600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>260800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2041600</v>
+      </c>
+      <c r="E42" s="3">
         <v>949500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>926600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>783600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>391400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>601500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>653800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>697600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>900500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>827200</v>
+      </c>
+      <c r="E43" s="3">
         <v>970500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>742800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>711900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>572500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>455600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>460300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>432300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>332000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>252100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,9 +2214,12 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,42 +2262,45 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>782700</v>
+      </c>
+      <c r="E45" s="3">
         <v>381300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>233000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>271800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>464800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>211000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>437400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>576400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,42 +2310,45 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8674800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5814100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4651100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4972100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2894200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2503600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2571600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2279100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2071300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>889100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,42 +2358,45 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1692700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1343000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1216200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1041700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2785300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1679900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1884600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1093900</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>1000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,42 +2406,45 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>428600</v>
+      </c>
+      <c r="E48" s="3">
         <v>604600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>817600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>920100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>926000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>875300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>225600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>87700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>92200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>82700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,42 +2454,45 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1284800</v>
+      </c>
+      <c r="E49" s="3">
         <v>1335200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1363700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1082700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>978600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>572300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>183200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>180100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>86800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74500</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,42 +2598,45 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E52" s="3">
         <v>82900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>87600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>95400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>77400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>74400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>64800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25500</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12428800</v>
+      </c>
+      <c r="E54" s="3">
         <v>9225200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8160700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8154200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7738200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5748000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4964500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3730800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2278500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1072900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>535200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>446200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,41 +2785,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>965900</v>
+      </c>
+      <c r="E57" s="3">
         <v>731700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>628400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>607300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>530900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>423100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>337800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>290600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>150800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>77600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,27 +2830,30 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E58" s="3">
         <v>71800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>62000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>37900</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -2728,14 +2861,14 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>5400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6100</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,42 +2878,45 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>761600</v>
+        <v>864500</v>
       </c>
       <c r="E59" s="3">
+        <v>770400</v>
+      </c>
+      <c r="F59" s="3">
         <v>623100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>698300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>643400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>529700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>755700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>775700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1167500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>730900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,42 +2926,45 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4607100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4520800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3757600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3668800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3547400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2737100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2460500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2233400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1323700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>814600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,42 +2974,45 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2071600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1874700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1798700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2025500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>705800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>698000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1133500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1201100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2880,42 +3022,45 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E62" s="3">
         <v>32100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>50000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>104200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>74400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19400</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,42 +3214,45 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6708800</v>
+      </c>
+      <c r="E66" s="3">
         <v>6436400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5594700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5744300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4307000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3462000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2567000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3445000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2538900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>839100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,42 +3474,45 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3151500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-4622500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3897600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3662000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4024500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3040100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2868100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2914300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1293300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-666600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,9 +3522,12 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5720100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2788800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2566000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2409900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3431200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2285900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2397500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>285800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-260400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>233800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>40600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>112400</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1178200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-588000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-459500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-710700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-208700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-89300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1482900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-584800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-234800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-212300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-75400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,41 +3886,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E83" s="3">
         <v>121600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>126100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>106900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>105200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>55200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2382200</v>
+      </c>
+      <c r="E89" s="3">
         <v>751600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>49200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>410600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>316800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>643000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>393900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>214900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>109600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-38800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-83600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-29900</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-95400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-151500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-143100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-43200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-44900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-40700</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1538500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-239900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-452100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-212700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-455000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-244600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-25200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-522300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-897300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-68400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,87 +4643,93 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>754700</v>
+      </c>
+      <c r="E100" s="3">
         <v>258600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-42700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1421600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>348600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-227800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>105300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>993900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>485900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>73400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>147100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-73000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>166700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>192200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-105200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>24700</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-67200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-34700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>20400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1725900</v>
+      </c>
+      <c r="E102" s="3">
         <v>697500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-278900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1811700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>105200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>195300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>474000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-333800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>171400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>399100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-33900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>68200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SPOT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>SPOT</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20178500</v>
+      </c>
+      <c r="E8" s="3">
         <v>16226300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14642400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12532900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10995100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9639100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7590600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6021300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4911100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3202900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1980400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1225100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>892400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>11317900</v>
+        <v>13725500</v>
       </c>
       <c r="E9" s="3">
-        <v>10831200</v>
+        <v>11321000</v>
       </c>
       <c r="F9" s="3">
+        <v>10832300</v>
+      </c>
+      <c r="G9" s="3">
         <v>9405800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8048400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7174300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5658200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4472200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3891700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2767800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1749700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1028600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>739300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4908400</v>
+        <v>6453000</v>
       </c>
       <c r="E10" s="3">
-        <v>3811200</v>
+        <v>4905300</v>
       </c>
       <c r="F10" s="3">
+        <v>3810100</v>
+      </c>
+      <c r="G10" s="3">
         <v>3127100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2946700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2464800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1932400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1549100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1019500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>435100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>230700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>196500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>153100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1529100</v>
+        <v>1635600</v>
       </c>
       <c r="E12" s="3">
-        <v>1692300</v>
+        <v>1538500</v>
       </c>
       <c r="F12" s="3">
+        <v>1775200</v>
+      </c>
+      <c r="G12" s="3">
         <v>1482300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1037200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1023900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>690200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>564500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>475500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>224600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>138800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>128700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>87300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,20 +999,23 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>44500</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>402300</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+        <v>14500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>273000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -1004,26 +1023,26 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>15700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1031,39 +1050,42 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E15" s="3">
         <v>71400</v>
       </c>
-      <c r="E15" s="3">
-        <v>99500</v>
-      </c>
       <c r="F15" s="3">
+        <v>174600</v>
+      </c>
+      <c r="G15" s="3">
         <v>182800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>144400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>135800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>97600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>64800</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1073,15 +1095,18 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14768600</v>
+        <v>17597700</v>
       </c>
       <c r="E17" s="3">
-        <v>14733100</v>
+        <v>14798600</v>
       </c>
       <c r="F17" s="3">
+        <v>14862400</v>
+      </c>
+      <c r="G17" s="3">
         <v>13237100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10888200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9997600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7656800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6070500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5365000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3583800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2220200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1440700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1009600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1457700</v>
+        <v>2580700</v>
       </c>
       <c r="E18" s="3">
-        <v>-90600</v>
+        <v>1427700</v>
       </c>
       <c r="F18" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-704300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>106900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-358400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-66200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-49200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-453900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-380800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-239900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-215700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-117200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,92 +1245,96 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>247700</v>
+      </c>
+      <c r="E20" s="3">
         <v>238100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>168000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-302400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-242200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>463600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>51600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>168300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1044700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-199600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>10200</v>
       </c>
       <c r="N20" s="3">
         <v>10200</v>
       </c>
       <c r="O20" s="3">
+        <v>10200</v>
+      </c>
+      <c r="P20" s="3">
         <v>44300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1291000</v>
+        <v>2398700</v>
       </c>
       <c r="E21" s="3">
-        <v>-159200</v>
+        <v>1261000</v>
       </c>
       <c r="F21" s="3">
+        <v>-213300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-219100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>493600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-686200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-180900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1433700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-539300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-199600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,39 +1344,42 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E22" s="3">
         <v>37300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>43800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>58000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>48300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2611200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1388300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-558200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-395400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>283200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-867300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-147000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-198100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1480500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-580500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-229700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-205500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-73000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E24" s="3">
         <v>210200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>64100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>321800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-156600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-108800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2597200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1178200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-588000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-459500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-710700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-208700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-89300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1482900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-584800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-234800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-212300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-75400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2597200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1178200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-588000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-459600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-710700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-208700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-89300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1483000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-584800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-234800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-212300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-75400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-247700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-238100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-168000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>302400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>242200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-463600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-51600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-168300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1044700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>199600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-10200</v>
       </c>
       <c r="N32" s="3">
         <v>-10200</v>
       </c>
       <c r="O32" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-44300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2597200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1178200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-588000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-459500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-710700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-208700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-89300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1482900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-584800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-234800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-212300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-75400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2597200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1178200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-588000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-459500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-710700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-208700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-89300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1482900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-584800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-234800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-212300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-75400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,140 +2159,147 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6173500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4949800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3442000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2653600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3120700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1408000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1195200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1020200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>572800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>819200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>609400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>232600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>260800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2886000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2041600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>949500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>926600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>783600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>391400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>601500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>653800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>697600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>900500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1077800</v>
+      </c>
+      <c r="E43" s="3">
         <v>827200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>970500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>742800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>711900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>572500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>455600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>460300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>432300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>332000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>252100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,9 +2309,12 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,45 +2360,48 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2098200</v>
+      </c>
+      <c r="E45" s="3">
         <v>782700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>381300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>233000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>271800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>464800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>211000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>437400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>576400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2313,45 +2411,48 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12323600</v>
+      </c>
+      <c r="E46" s="3">
         <v>8674800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5814100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4651100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4972100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2894200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2503600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2571600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2279100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2071300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>889100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2361,45 +2462,48 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2560800</v>
+      </c>
+      <c r="E47" s="3">
         <v>1692700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1343000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1216200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1041700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2785300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1679900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1884600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1093900</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>1000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,45 +2513,48 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>495500</v>
+      </c>
+      <c r="E48" s="3">
         <v>428600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>604600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>817600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>920100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>926000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>875300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>225600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>87700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>92200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>82700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,45 +2564,48 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1305600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1284800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1335200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1363700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1082700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>978600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>572300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>183200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>180100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>86800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>74500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,45 +2717,48 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E52" s="3">
         <v>70400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>82900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>83400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>87600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>95400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>77400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>74400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>64800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,9 +2768,12 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17629400</v>
+      </c>
+      <c r="E54" s="3">
         <v>12428800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9225200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8160700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8154200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7738200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5748000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4964500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3730800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2278500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1072900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>535200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>446200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,44 +2915,45 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>919300</v>
+      </c>
+      <c r="E57" s="3">
         <v>965900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>731700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>628400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>607300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>530900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>423100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>337800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>290600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>150800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>77600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2833,30 +2963,33 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1788200</v>
+      </c>
+      <c r="E58" s="3">
         <v>77600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>71800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>62000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>50000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>37900</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -2864,14 +2997,14 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>5400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6100</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,45 +3014,48 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1027400</v>
+      </c>
+      <c r="E59" s="3">
         <v>864500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>770400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>623100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>698300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>643400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>529700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>755700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>775700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1167500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>730900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,45 +3065,48 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7144500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4607100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4520800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3757600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3668800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3547400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2737100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2460500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2233400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1323700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>814600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,45 +3116,48 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>508400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2071600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1874700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1798700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2025500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>705800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>698000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1133500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1201100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3025,45 +3167,48 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E62" s="3">
         <v>8300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>32100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>50000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>53800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>104200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>74400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19400</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,45 +3371,48 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7850200</v>
+      </c>
+      <c r="E66" s="3">
         <v>6708800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6436400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5594700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5744300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4307000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3462000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2567000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3445000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2538900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>839100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3265,9 +3422,12 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,45 +3647,48 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-976900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3151500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-4622500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3897600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3662000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4024500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3040100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2868100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2914300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1293300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-666600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,9 +3698,12 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9779300</v>
+      </c>
+      <c r="E76" s="3">
         <v>5720100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2788800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2566000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2409900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3431200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2285900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2397500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>285800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-260400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>233800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>112400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2597200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1178200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-588000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-459500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-710700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-208700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-89300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1482900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-584800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-234800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-212300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-75400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,44 +4084,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E83" s="3">
         <v>88000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>121600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>126100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>106900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>105200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>55200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30600</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,9 +4132,12 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3443700</v>
+      </c>
+      <c r="E89" s="3">
         <v>2382200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>751600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>49200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>410600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>316800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>643000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>393900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>214900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>109600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-38800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-83600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-29900</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-17600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-96700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-95400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-151500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-143100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-43200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-44900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-40700</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2095800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1538500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-239900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-452100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-212700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-455000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-244600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-25200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-522300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-897300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-68400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,93 +4888,99 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-447300</v>
+      </c>
+      <c r="E100" s="3">
         <v>754700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>258600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-42700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1421600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>348600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-227800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>105300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>993900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>485900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>73400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>147100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-340500</v>
+      </c>
+      <c r="E101" s="3">
         <v>127300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-73000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>166700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>192200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-105200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24700</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-67200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-34700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>20400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4742,55 +4990,61 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>560100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1725900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>697500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-278900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1811700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>105200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>195300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>474000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-333800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>171400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>399100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-33900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>68200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
